--- a/data/SEMANA ATUAL/rodada 8/TAPETES MP.xlsx
+++ b/data/SEMANA ATUAL/rodada 8/TAPETES MP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="280">
   <si>
     <t>Sigla Loja</t>
   </si>
@@ -34,6 +34,15 @@
     <t>20/08/2026 (Qui)</t>
   </si>
   <si>
+    <t>21/08/2026 (Sex)</t>
+  </si>
+  <si>
+    <t>22/08/2026 (Sáb)</t>
+  </si>
+  <si>
+    <t>23/08/2026 (Dom)</t>
+  </si>
+  <si>
     <t>ABNO-RJ</t>
   </si>
   <si>
@@ -202,6 +211,9 @@
     <t>CDEM-SP</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>CDIA-DF</t>
   </si>
   <si>
@@ -568,9 +580,6 @@
     <t>PIND-SP</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>PIRA-SP</t>
   </si>
   <si>
@@ -839,6 +848,9 @@
   </si>
   <si>
     <t>ZBND-MG</t>
+  </si>
+  <si>
+    <t>ZTMP-SP</t>
   </si>
   <si>
     <t>ZVJD-SP</t>
@@ -1207,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F270"/>
+  <dimension ref="A1:I271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1215,7 +1227,7 @@
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1234,10 +1246,19 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>1974.89</v>
@@ -1246,15 +1267,24 @@
         <v>3404.169999999999</v>
       </c>
       <c r="E2" s="1">
-        <v>3150.879999999999</v>
+        <v>3150.880000000001</v>
       </c>
       <c r="F2" s="1">
         <v>2512.69</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="1">
+        <v>3906.46</v>
+      </c>
+      <c r="H2" s="1">
+        <v>2127.64</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1918.88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>4633.16</v>
@@ -1268,10 +1298,19 @@
       <c r="F3" s="1">
         <v>2481.73</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="1">
+        <v>3846.350000000001</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2780.49</v>
+      </c>
+      <c r="I3" s="1">
+        <v>4308.79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2738.29</v>
@@ -1280,32 +1319,50 @@
         <v>6127.129999999998</v>
       </c>
       <c r="E4" s="1">
-        <v>2816.199999999999</v>
+        <v>2816.2</v>
       </c>
       <c r="F4" s="1">
         <v>2188.4</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="1">
+        <v>3542.509999999999</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3131.86</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2470.89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>2171.19</v>
       </c>
       <c r="D5" s="1">
-        <v>3349.139999999999</v>
+        <v>3349.14</v>
       </c>
       <c r="E5" s="1">
         <v>1219.19</v>
       </c>
       <c r="F5" s="1">
-        <v>3512.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>3512.799999999999</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2415.88</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2959.37</v>
+      </c>
+      <c r="I5" s="1">
+        <v>4519.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1">
         <v>2753.8</v>
@@ -1314,32 +1371,50 @@
         <v>3103.079999999999</v>
       </c>
       <c r="E6" s="1">
-        <v>3101.969999999999</v>
+        <v>3101.97</v>
       </c>
       <c r="F6" s="1">
-        <v>3498.059999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>3498.06</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1993.82</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4058.649999999999</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2814.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1">
-        <v>4022.159999999999</v>
+        <v>4022.16</v>
       </c>
       <c r="D7" s="1">
         <v>3319.969999999999</v>
       </c>
       <c r="E7" s="1">
-        <v>3541.989999999999</v>
+        <v>3541.99</v>
       </c>
       <c r="F7" s="1">
         <v>2856.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="1">
+        <v>3882.199999999999</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2679.29</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3314.329999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>1670.45</v>
@@ -1353,10 +1428,19 @@
       <c r="F8" s="1">
         <v>767.6799999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="1">
+        <v>2516.21</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1708.63</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1695.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1">
         <v>2176.14</v>
@@ -1370,10 +1454,19 @@
       <c r="F9" s="1">
         <v>2449.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1">
+        <v>1723.13</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2553.170000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2539.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1">
         <v>1138.37</v>
@@ -1387,13 +1480,22 @@
       <c r="F10" s="1">
         <v>831.8800000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="1">
+        <v>1961.24</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1316.29</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1261.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1">
-        <v>4831.979999999999</v>
+        <v>4831.98</v>
       </c>
       <c r="D11" s="1">
         <v>4798.16</v>
@@ -1402,12 +1504,21 @@
         <v>3796.57</v>
       </c>
       <c r="F11" s="1">
-        <v>4528.959999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>4528.959999999999</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4194.9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5243.82</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6036.389999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1">
         <v>589.9</v>
@@ -1421,27 +1532,45 @@
       <c r="F12" s="1">
         <v>296.96</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="1">
+        <v>686.99</v>
+      </c>
+      <c r="H12" s="1">
+        <v>462.36</v>
+      </c>
+      <c r="I12" s="1">
+        <v>658.5599999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1">
         <v>1596.45</v>
       </c>
       <c r="D13" s="1">
-        <v>3319.59</v>
+        <v>3319.589999999999</v>
       </c>
       <c r="E13" s="1">
-        <v>2530.87</v>
+        <v>2530.869999999999</v>
       </c>
       <c r="F13" s="1">
-        <v>3102.59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>3102.589999999999</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2845.599999999999</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2499.35</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2002.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1">
         <v>2783.88</v>
@@ -1455,61 +1584,97 @@
       <c r="F14" s="1">
         <v>2998.51</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="1">
+        <v>2034.57</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3338.759999999999</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2481.98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
-        <v>4807.679999999999</v>
+        <v>4807.68</v>
       </c>
       <c r="D15" s="1">
-        <v>5319.419999999999</v>
+        <v>5319.419999999998</v>
       </c>
       <c r="E15" s="1">
         <v>4824.969999999999</v>
       </c>
       <c r="F15" s="1">
-        <v>5216.289999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>5216.289999999998</v>
+      </c>
+      <c r="G15" s="1">
+        <v>6042.349999999998</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5387.189999999998</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5237.54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1">
-        <v>822.0500000000002</v>
+        <v>822.05</v>
       </c>
       <c r="D16" s="1">
         <v>418.32</v>
       </c>
       <c r="E16" s="1">
-        <v>563.9400000000001</v>
+        <v>563.9399999999999</v>
       </c>
       <c r="F16" s="1">
-        <v>776.9100000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>776.91</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1073.09</v>
+      </c>
+      <c r="H16" s="1">
+        <v>861.61</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1730.74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
         <v>3544.02</v>
       </c>
       <c r="D17" s="1">
-        <v>2779.219999999999</v>
+        <v>2779.22</v>
       </c>
       <c r="E17" s="1">
-        <v>2909.6</v>
+        <v>2909.599999999999</v>
       </c>
       <c r="F17" s="1">
-        <v>4942.239999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>4942.239999999999</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2928.239999999999</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2894.5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>3445.319999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1">
         <v>1254.16</v>
@@ -1523,10 +1688,19 @@
       <c r="F18" s="1">
         <v>1542.48</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="1">
+        <v>722.88</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2510.439999999999</v>
+      </c>
+      <c r="I18" s="1">
+        <v>3076.059999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1">
         <v>2866.17</v>
@@ -1538,32 +1712,50 @@
         <v>4042.66</v>
       </c>
       <c r="F19" s="1">
-        <v>3999.069999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>3999.07</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2868.18</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2331.599999999999</v>
+      </c>
+      <c r="I19" s="1">
+        <v>3473.14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1">
         <v>2965.52</v>
       </c>
       <c r="D20" s="1">
-        <v>2714.339999999999</v>
+        <v>2714.34</v>
       </c>
       <c r="E20" s="1">
         <v>2801.58</v>
       </c>
       <c r="F20" s="1">
-        <v>2460.739999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>2460.74</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2497.6</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2716.32</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3563.139999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1">
-        <v>3895.149999999999</v>
+        <v>3895.15</v>
       </c>
       <c r="D21" s="1">
         <v>1157.97</v>
@@ -1574,27 +1766,45 @@
       <c r="F21" s="1">
         <v>2279.11</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="1">
+        <v>4379.22</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5163.349999999999</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2238.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1">
         <v>779.99</v>
       </c>
       <c r="D22" s="1">
-        <v>443.93</v>
+        <v>443.9300000000001</v>
       </c>
       <c r="E22" s="1">
-        <v>980.8699999999999</v>
+        <v>980.87</v>
       </c>
       <c r="F22" s="1">
-        <v>489.6900000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>489.69</v>
+      </c>
+      <c r="G22" s="1">
+        <v>868.8800000000001</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1289.82</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1273.82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1">
         <v>474.92</v>
@@ -1608,10 +1818,19 @@
       <c r="F23" s="1">
         <v>370.49</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="1">
+        <v>1013.31</v>
+      </c>
+      <c r="H23" s="1">
+        <v>257.95</v>
+      </c>
+      <c r="I23" s="1">
+        <v>914.8500000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C24" s="1">
         <v>632.51</v>
@@ -1625,10 +1844,19 @@
       <c r="F24" s="1">
         <v>955.5599999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="1">
+        <v>1293.85</v>
+      </c>
+      <c r="H24" s="1">
+        <v>977.9000000000001</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1859.79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1">
         <v>974.1</v>
@@ -1642,13 +1870,22 @@
       <c r="F25" s="1">
         <v>633</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="1">
+        <v>1097.73</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1081.64</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1168.12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1">
-        <v>3509.359999999999</v>
+        <v>3509.36</v>
       </c>
       <c r="D26" s="1">
         <v>3262.27</v>
@@ -1657,12 +1894,21 @@
         <v>3055.829999999999</v>
       </c>
       <c r="F26" s="1">
-        <v>4189.339999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>4189.339999999999</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2805.27</v>
+      </c>
+      <c r="H26" s="1">
+        <v>4039.91</v>
+      </c>
+      <c r="I26" s="1">
+        <v>3834.319999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C27" s="1">
         <v>1961.56</v>
@@ -1676,47 +1922,74 @@
       <c r="F27" s="1">
         <v>1592.85</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="1">
+        <v>1201.36</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1392.07</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2475.239999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C28" s="1">
         <v>5007.719999999999</v>
       </c>
       <c r="D28" s="1">
-        <v>6434.349999999999</v>
+        <v>6434.35</v>
       </c>
       <c r="E28" s="1">
-        <v>3964.36</v>
+        <v>3964.359999999999</v>
       </c>
       <c r="F28" s="1">
         <v>5852.06</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="1">
+        <v>5705.819999999999</v>
+      </c>
+      <c r="H28" s="1">
+        <v>4799.249999999999</v>
+      </c>
+      <c r="I28" s="1">
+        <v>3078.349999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1">
-        <v>5027.28</v>
+        <v>5027.279999999999</v>
       </c>
       <c r="D29" s="1">
-        <v>4131.209999999999</v>
+        <v>4131.21</v>
       </c>
       <c r="E29" s="1">
-        <v>3856.869999999999</v>
+        <v>3856.87</v>
       </c>
       <c r="F29" s="1">
-        <v>4018.729999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>4018.73</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4722.92</v>
+      </c>
+      <c r="H29" s="1">
+        <v>3963.24</v>
+      </c>
+      <c r="I29" s="1">
+        <v>4307.509999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C30" s="1">
-        <v>2419.97</v>
+        <v>2419.969999999999</v>
       </c>
       <c r="D30" s="1">
         <v>2215.24</v>
@@ -1727,10 +2000,19 @@
       <c r="F30" s="1">
         <v>2191.85</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="1">
+        <v>2564.75</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1647.37</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2763.639999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C31" s="1">
         <v>672.29</v>
@@ -1744,13 +2026,22 @@
       <c r="F31" s="1">
         <v>784.84</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="1">
+        <v>712.9100000000001</v>
+      </c>
+      <c r="H31" s="1">
+        <v>984.67</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1004.05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C32" s="1">
-        <v>6787.979999999998</v>
+        <v>6787.98</v>
       </c>
       <c r="D32" s="1">
         <v>6545.719999999998</v>
@@ -1761,33 +2052,51 @@
       <c r="F32" s="1">
         <v>5953.94</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" s="1">
+        <v>5362.549999999999</v>
+      </c>
+      <c r="H32" s="1">
+        <v>5325.429999999999</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5258.889999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C33" s="1">
-        <v>6318.209999999999</v>
+        <v>6318.209999999997</v>
       </c>
       <c r="D33" s="1">
-        <v>8065.639999999998</v>
+        <v>8065.639999999999</v>
       </c>
       <c r="E33" s="1">
         <v>6661.48</v>
       </c>
       <c r="F33" s="1">
-        <v>5472.07</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>5472.069999999999</v>
+      </c>
+      <c r="G33" s="1">
+        <v>5951.32</v>
+      </c>
+      <c r="H33" s="1">
+        <v>6947.479999999999</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5404.979999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C34" s="1">
         <v>10322.84</v>
       </c>
       <c r="D34" s="1">
-        <v>9560.119999999997</v>
+        <v>9560.119999999999</v>
       </c>
       <c r="E34" s="1">
         <v>6788.659999999999</v>
@@ -1795,10 +2104,19 @@
       <c r="F34" s="1">
         <v>8485.92</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="1">
+        <v>6857.59</v>
+      </c>
+      <c r="H34" s="1">
+        <v>9591.299999999999</v>
+      </c>
+      <c r="I34" s="1">
+        <v>11435.77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C35" s="1">
         <v>1008.32</v>
@@ -1812,13 +2130,22 @@
       <c r="F35" s="1">
         <v>779.97</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="1">
+        <v>941.84</v>
+      </c>
+      <c r="H35" s="1">
+        <v>888.8400000000001</v>
+      </c>
+      <c r="I35" s="1">
+        <v>856.4000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C36" s="1">
-        <v>4151.019999999999</v>
+        <v>4151.02</v>
       </c>
       <c r="D36" s="1">
         <v>2055.31</v>
@@ -1829,27 +2156,45 @@
       <c r="F36" s="1">
         <v>2260.21</v>
       </c>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="1">
+        <v>2620.979999999999</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2996.84</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2583.69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C37" s="1">
-        <v>6562.45</v>
+        <v>6562.449999999999</v>
       </c>
       <c r="D37" s="1">
-        <v>7839.710000000001</v>
+        <v>7839.709999999997</v>
       </c>
       <c r="E37" s="1">
         <v>4970.280000000001</v>
       </c>
       <c r="F37" s="1">
-        <v>5571.760000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>5571.76</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5757.309999999999</v>
+      </c>
+      <c r="H37" s="1">
+        <v>4798.35</v>
+      </c>
+      <c r="I37" s="1">
+        <v>6373.199999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C38" s="1">
         <v>762.86</v>
@@ -1861,12 +2206,21 @@
         <v>597.13</v>
       </c>
       <c r="F38" s="1">
-        <v>679.77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>679.7700000000001</v>
+      </c>
+      <c r="G38" s="1">
+        <v>701.86</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1228.75</v>
+      </c>
+      <c r="I38" s="1">
+        <v>823.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C39" s="1">
         <v>649.9200000000001</v>
@@ -1880,16 +2234,25 @@
       <c r="F39" s="1">
         <v>1604.82</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="1">
+        <v>962.84</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1507.29</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2207.68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C40" s="1">
         <v>588.9299999999999</v>
       </c>
       <c r="D40" s="1">
-        <v>867.0500000000002</v>
+        <v>867.05</v>
       </c>
       <c r="E40" s="1">
         <v>934.55</v>
@@ -1897,10 +2260,19 @@
       <c r="F40" s="1">
         <v>738.12</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="1">
+        <v>928.73</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1044.89</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1289.13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C41" s="1">
         <v>1562.75</v>
@@ -1914,27 +2286,45 @@
       <c r="F41" s="1">
         <v>1942.52</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="1">
+        <v>2954.04</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1757.22</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2033.83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C42" s="1">
         <v>4305.099999999999</v>
       </c>
       <c r="D42" s="1">
-        <v>3162.55</v>
+        <v>3162.549999999999</v>
       </c>
       <c r="E42" s="1">
-        <v>2455.07</v>
+        <v>2275.09</v>
       </c>
       <c r="F42" s="1">
-        <v>3761.979999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>3761.98</v>
+      </c>
+      <c r="G42" s="1">
+        <v>3121.15</v>
+      </c>
+      <c r="H42" s="1">
+        <v>3832.57</v>
+      </c>
+      <c r="I42" s="1">
+        <v>4413.699999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C43" s="1">
         <v>741.8900000000001</v>
@@ -1948,13 +2338,22 @@
       <c r="F43" s="1">
         <v>296.57</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="1">
+        <v>508.41</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1036.83</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1005.79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C44" s="1">
-        <v>888.8899999999999</v>
+        <v>888.89</v>
       </c>
       <c r="D44" s="1">
         <v>1335.19</v>
@@ -1965,10 +2364,19 @@
       <c r="F44" s="1">
         <v>2075.35</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="1">
+        <v>2142.75</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1885.44</v>
+      </c>
+      <c r="I44" s="1">
+        <v>2009.89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C45" s="1">
         <v>4287.559999999999</v>
@@ -1977,32 +2385,50 @@
         <v>5111.7</v>
       </c>
       <c r="E45" s="1">
-        <v>4388.149999999998</v>
+        <v>4388.15</v>
       </c>
       <c r="F45" s="1">
-        <v>4939.429999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>4939.429999999999</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3499.27</v>
+      </c>
+      <c r="H45" s="1">
+        <v>4751.179999999999</v>
+      </c>
+      <c r="I45" s="1">
+        <v>3193.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C46" s="1">
-        <v>3304.559999999999</v>
+        <v>3304.56</v>
       </c>
       <c r="D46" s="1">
         <v>4271.119999999999</v>
       </c>
       <c r="E46" s="1">
-        <v>5119.369999999999</v>
+        <v>5119.369999999998</v>
       </c>
       <c r="F46" s="1">
-        <v>3564.619999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>3564.619999999998</v>
+      </c>
+      <c r="G46" s="1">
+        <v>3751.03</v>
+      </c>
+      <c r="H46" s="1">
+        <v>6143.999999999999</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5873.16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C47" s="1">
         <v>1369.62</v>
@@ -2016,16 +2442,25 @@
       <c r="F47" s="1">
         <v>2186.18</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" s="1">
+        <v>1216.87</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1077.88</v>
+      </c>
+      <c r="I47" s="1">
+        <v>822.3399999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C48" s="1">
         <v>1924.7</v>
       </c>
       <c r="D48" s="1">
-        <v>2434.169999999999</v>
+        <v>2434.17</v>
       </c>
       <c r="E48" s="1">
         <v>3112.76</v>
@@ -2033,10 +2468,19 @@
       <c r="F48" s="1">
         <v>1143.79</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="1">
+        <v>1927.87</v>
+      </c>
+      <c r="H48" s="1">
+        <v>3468.34</v>
+      </c>
+      <c r="I48" s="1">
+        <v>2899.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C49" s="1">
         <v>3240.139999999999</v>
@@ -2050,13 +2494,22 @@
       <c r="F49" s="1">
         <v>3283.609999999999</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="1">
+        <v>4879.44</v>
+      </c>
+      <c r="H49" s="1">
+        <v>3892.02</v>
+      </c>
+      <c r="I49" s="1">
+        <v>4116.259999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C50" s="1">
-        <v>958.88</v>
+        <v>958.8800000000001</v>
       </c>
       <c r="D50" s="1">
         <v>656.91</v>
@@ -2067,16 +2520,25 @@
       <c r="F50" s="1">
         <v>528.9299999999999</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="1">
+        <v>401.96</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1146.69</v>
+      </c>
+      <c r="I50" s="1">
+        <v>273.96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C51" s="1">
         <v>618.2</v>
       </c>
       <c r="D51" s="1">
-        <v>953.3000000000002</v>
+        <v>953.3</v>
       </c>
       <c r="E51" s="1">
         <v>741.4299999999999</v>
@@ -2084,10 +2546,19 @@
       <c r="F51" s="1">
         <v>1002.4</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" s="1">
+        <v>1451.91</v>
+      </c>
+      <c r="H51" s="1">
+        <v>1196.53</v>
+      </c>
+      <c r="I51" s="1">
+        <v>971.0300000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C52" s="1">
         <v>1578.49</v>
@@ -2101,10 +2572,19 @@
       <c r="F52" s="1">
         <v>1481.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="1">
+        <v>948.09</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1554.72</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1005.08</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C53" s="1">
         <v>2023.88</v>
@@ -2113,15 +2593,24 @@
         <v>1553</v>
       </c>
       <c r="E53" s="1">
-        <v>3061.179999999999</v>
+        <v>3061.18</v>
       </c>
       <c r="F53" s="1">
         <v>2435.07</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="1">
+        <v>2620.129999999999</v>
+      </c>
+      <c r="H53" s="1">
+        <v>2208.1</v>
+      </c>
+      <c r="I53" s="1">
+        <v>2159.09</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C54" s="1">
         <v>924.2800000000001</v>
@@ -2135,10 +2624,19 @@
       <c r="F54" s="1">
         <v>771.92</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="1">
+        <v>875.2599999999999</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1029.93</v>
+      </c>
+      <c r="I54" s="1">
+        <v>386.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C55" s="1">
         <v>1181.8</v>
@@ -2152,16 +2650,25 @@
       <c r="F55" s="1">
         <v>1888.78</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="1">
+        <v>701.75</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1436.75</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1668.69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C56" s="1">
         <v>1776.76</v>
       </c>
       <c r="D56" s="1">
-        <v>2260.01</v>
+        <v>2260.009999999999</v>
       </c>
       <c r="E56" s="1">
         <v>2321.39</v>
@@ -2169,27 +2676,45 @@
       <c r="F56" s="1">
         <v>1366.72</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="1">
+        <v>2623.83</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1976.32</v>
+      </c>
+      <c r="I56" s="1">
+        <v>2612.61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C57" s="1">
-        <v>7948.659999999999</v>
+        <v>7948.66</v>
       </c>
       <c r="D57" s="1">
         <v>8324.700000000001</v>
       </c>
       <c r="E57" s="1">
-        <v>8700.76</v>
+        <v>8700.759999999998</v>
       </c>
       <c r="F57" s="1">
-        <v>5730.759999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>5730.76</v>
+      </c>
+      <c r="G57" s="1">
+        <v>3784.489999999999</v>
+      </c>
+      <c r="H57" s="1">
+        <v>4735.959999999999</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C58" s="1">
         <v>1320.14</v>
@@ -2203,27 +2728,45 @@
       <c r="F58" s="1">
         <v>905.8099999999999</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="1">
+        <v>990.84</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1332.19</v>
+      </c>
+      <c r="I58" s="1">
+        <v>907.95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C59" s="1">
         <v>3369.98</v>
       </c>
       <c r="D59" s="1">
-        <v>4010.339999999999</v>
+        <v>4010.34</v>
       </c>
       <c r="E59" s="1">
-        <v>3971.22</v>
+        <v>3971.219999999999</v>
       </c>
       <c r="F59" s="1">
         <v>4088.89</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="1">
+        <v>5226.749999999998</v>
+      </c>
+      <c r="H59" s="1">
+        <v>998.13</v>
+      </c>
+      <c r="I59" s="1">
+        <v>1893.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C60" s="1">
         <v>1279.46</v>
@@ -2237,13 +2780,22 @@
       <c r="F60" s="1">
         <v>1317.25</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="1">
+        <v>579.4200000000001</v>
+      </c>
+      <c r="H60" s="1">
+        <v>1050.62</v>
+      </c>
+      <c r="I60" s="1">
+        <v>610.9299999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C61" s="1">
-        <v>2309.55</v>
+        <v>2309.549999999999</v>
       </c>
       <c r="D61" s="1">
         <v>2281.23</v>
@@ -2254,10 +2806,19 @@
       <c r="F61" s="1">
         <v>2823.309999999999</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="1">
+        <v>3009.849999999999</v>
+      </c>
+      <c r="H61" s="1">
+        <v>3273.439999999999</v>
+      </c>
+      <c r="I61" s="1">
+        <v>1437.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C62" s="1">
         <v>1036.45</v>
@@ -2269,12 +2830,21 @@
         <v>841.3900000000001</v>
       </c>
       <c r="F62" s="1">
-        <v>674.0300000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>674.03</v>
+      </c>
+      <c r="G62" s="1">
+        <v>376.92</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1260.02</v>
+      </c>
+      <c r="I62" s="1">
+        <v>531.52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C63" s="1">
         <v>2661.39</v>
@@ -2283,21 +2853,30 @@
         <v>4706.589999999999</v>
       </c>
       <c r="E63" s="1">
-        <v>6308.319999999998</v>
+        <v>6308.32</v>
       </c>
       <c r="F63" s="1">
-        <v>4187.35</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>4187.349999999999</v>
+      </c>
+      <c r="G63" s="1">
+        <v>3815.239999999999</v>
+      </c>
+      <c r="H63" s="1">
+        <v>3822.159999999999</v>
+      </c>
+      <c r="I63" s="1">
+        <v>4238.27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C64" s="1">
-        <v>826.29</v>
+        <v>826.2900000000001</v>
       </c>
       <c r="D64" s="1">
-        <v>888.85</v>
+        <v>888.8499999999999</v>
       </c>
       <c r="E64" s="1">
         <v>757.64</v>
@@ -2305,10 +2884,19 @@
       <c r="F64" s="1">
         <v>2443.06</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="1">
+        <v>516.13</v>
+      </c>
+      <c r="H64" s="1">
+        <v>964.89</v>
+      </c>
+      <c r="I64" s="1">
+        <v>443.78</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C65" s="1">
         <v>874.47</v>
@@ -2322,10 +2910,19 @@
       <c r="F65" s="1">
         <v>1130.9</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="1">
+        <v>1509.43</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1409.83</v>
+      </c>
+      <c r="I65" s="1">
+        <v>763.85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C66" s="1">
         <v>2273.05</v>
@@ -2334,18 +2931,27 @@
         <v>926.35</v>
       </c>
       <c r="E66" s="1">
-        <v>970.6700000000001</v>
+        <v>970.67</v>
       </c>
       <c r="F66" s="1">
         <v>1180.06</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="1">
+        <v>846.55</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1492.96</v>
+      </c>
+      <c r="I66" s="1">
+        <v>622.66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C67" s="1">
-        <v>841.0200000000001</v>
+        <v>841.02</v>
       </c>
       <c r="D67" s="1">
         <v>569.14</v>
@@ -2356,10 +2962,19 @@
       <c r="F67" s="1">
         <v>879.73</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="1">
+        <v>820.8800000000001</v>
+      </c>
+      <c r="H67" s="1">
+        <v>479.4399999999999</v>
+      </c>
+      <c r="I67" s="1">
+        <v>755.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C68" s="1">
         <v>931.27</v>
@@ -2373,10 +2988,19 @@
       <c r="F68" s="1">
         <v>1601.17</v>
       </c>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68" s="1">
+        <v>2084.74</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1804.18</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1080.84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C69" s="1">
         <v>1018.44</v>
@@ -2390,27 +3014,45 @@
       <c r="F69" s="1">
         <v>1814.19</v>
       </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" s="1">
+        <v>1179.56</v>
+      </c>
+      <c r="H69" s="1">
+        <v>705.9299999999999</v>
+      </c>
+      <c r="I69" s="1">
+        <v>982.6100000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C70" s="1">
-        <v>3392.609999999999</v>
+        <v>3392.61</v>
       </c>
       <c r="D70" s="1">
         <v>4248.229999999999</v>
       </c>
       <c r="E70" s="1">
-        <v>3366.83</v>
+        <v>3366.829999999999</v>
       </c>
       <c r="F70" s="1">
         <v>3182.02</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="1">
+        <v>3817.159999999999</v>
+      </c>
+      <c r="H70" s="1">
+        <v>3285.12</v>
+      </c>
+      <c r="I70" s="1">
+        <v>3970.189999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C71" s="1">
         <v>1053.79</v>
@@ -2424,10 +3066,19 @@
       <c r="F71" s="1">
         <v>606.3200000000001</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71" s="1">
+        <v>948.62</v>
+      </c>
+      <c r="H71" s="1">
+        <v>890.0500000000002</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1436.77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C72" s="1">
         <v>1606.68</v>
@@ -2441,13 +3092,22 @@
       <c r="F72" s="1">
         <v>2402.34</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="1">
+        <v>1746.62</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1382.01</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1780.75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C73" s="1">
-        <v>3214.03</v>
+        <v>3214.029999999999</v>
       </c>
       <c r="D73" s="1">
         <v>2129.74</v>
@@ -2456,12 +3116,21 @@
         <v>2491.26</v>
       </c>
       <c r="F73" s="1">
-        <v>3771.359999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>3771.36</v>
+      </c>
+      <c r="G73" s="1">
+        <v>3079.82</v>
+      </c>
+      <c r="H73" s="1">
+        <v>2046.74</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1525.83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C74" s="1">
         <v>891.36</v>
@@ -2473,12 +3142,21 @@
         <v>1593.58</v>
       </c>
       <c r="F74" s="1">
-        <v>871.67</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>871.6700000000001</v>
+      </c>
+      <c r="G74" s="1">
+        <v>994.55</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1515.37</v>
+      </c>
+      <c r="I74" s="1">
+        <v>903.71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C75" s="1">
         <v>1822.07</v>
@@ -2490,12 +3168,21 @@
         <v>1131.73</v>
       </c>
       <c r="F75" s="1">
-        <v>632.3000000000002</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>632.3</v>
+      </c>
+      <c r="G75" s="1">
+        <v>1288.04</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1185.78</v>
+      </c>
+      <c r="I75" s="1">
+        <v>1199.18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C76" s="1">
         <v>2530.559999999999</v>
@@ -2504,15 +3191,24 @@
         <v>3345.23</v>
       </c>
       <c r="E76" s="1">
-        <v>3483.919999999998</v>
+        <v>3483.920000000001</v>
       </c>
       <c r="F76" s="1">
-        <v>2655.93</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>2655.929999999999</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2430.579999999999</v>
+      </c>
+      <c r="H76" s="1">
+        <v>2643.9</v>
+      </c>
+      <c r="I76" s="1">
+        <v>2187.34</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C77" s="1">
         <v>2000.36</v>
@@ -2526,16 +3222,25 @@
       <c r="F77" s="1">
         <v>1130.11</v>
       </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="G77" s="1">
+        <v>1144.83</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1724.5</v>
+      </c>
+      <c r="I77" s="1">
+        <v>2457.179999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C78" s="1">
-        <v>516.4699999999999</v>
+        <v>516.47</v>
       </c>
       <c r="D78" s="1">
-        <v>510.43</v>
+        <v>510.4300000000001</v>
       </c>
       <c r="E78" s="1">
         <v>385.75</v>
@@ -2543,10 +3248,19 @@
       <c r="F78" s="1">
         <v>1106.04</v>
       </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="G78" s="1">
+        <v>650.59</v>
+      </c>
+      <c r="H78" s="1">
+        <v>624.64</v>
+      </c>
+      <c r="I78" s="1">
+        <v>1079.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C79" s="1">
         <v>2015.86</v>
@@ -2560,27 +3274,45 @@
       <c r="F79" s="1">
         <v>1256.99</v>
       </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="G79" s="1">
+        <v>1310.99</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2131.31</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1023.52</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C80" s="1">
-        <v>923.8900000000001</v>
+        <v>923.89</v>
       </c>
       <c r="D80" s="1">
-        <v>2432.71</v>
+        <v>2432.709999999999</v>
       </c>
       <c r="E80" s="1">
         <v>1933.2</v>
       </c>
       <c r="F80" s="1">
-        <v>3111.699999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>3111.7</v>
+      </c>
+      <c r="G80" s="1">
+        <v>1798.83</v>
+      </c>
+      <c r="H80" s="1">
+        <v>2110.66</v>
+      </c>
+      <c r="I80" s="1">
+        <v>2176.94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C81" s="1">
         <v>1309.37</v>
@@ -2594,10 +3326,19 @@
       <c r="F81" s="1">
         <v>1779.14</v>
       </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81" s="1">
+        <v>1481.67</v>
+      </c>
+      <c r="H81" s="1">
+        <v>2005.68</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1183.14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C82" s="1">
         <v>945.34</v>
@@ -2611,10 +3352,19 @@
       <c r="F82" s="1">
         <v>1407.57</v>
       </c>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="G82" s="1">
+        <v>1034.56</v>
+      </c>
+      <c r="H82" s="1">
+        <v>947.6700000000001</v>
+      </c>
+      <c r="I82" s="1">
+        <v>421.16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C83" s="1">
         <v>2049.68</v>
@@ -2628,10 +3378,19 @@
       <c r="F83" s="1">
         <v>1542.61</v>
       </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83" s="1">
+        <v>1223.16</v>
+      </c>
+      <c r="H83" s="1">
+        <v>2054.12</v>
+      </c>
+      <c r="I83" s="1">
+        <v>2935.560000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C84" s="1">
         <v>2238.46</v>
@@ -2645,27 +3404,45 @@
       <c r="F84" s="1">
         <v>2124.98</v>
       </c>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="G84" s="1">
+        <v>1365.4</v>
+      </c>
+      <c r="H84" s="1">
+        <v>1937.25</v>
+      </c>
+      <c r="I84" s="1">
+        <v>1364.84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C85" s="1">
-        <v>4991.909999999999</v>
+        <v>4991.91</v>
       </c>
       <c r="D85" s="1">
-        <v>5802.559999999999</v>
+        <v>5802.56</v>
       </c>
       <c r="E85" s="1">
-        <v>5464.29</v>
+        <v>5464.289999999998</v>
       </c>
       <c r="F85" s="1">
         <v>4257.219999999999</v>
       </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="G85" s="1">
+        <v>4842.009999999999</v>
+      </c>
+      <c r="H85" s="1">
+        <v>7168.92</v>
+      </c>
+      <c r="I85" s="1">
+        <v>6384.679999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C86" s="1">
         <v>1800.15</v>
@@ -2679,16 +3456,25 @@
       <c r="F86" s="1">
         <v>2399.96</v>
       </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86" s="1">
+        <v>1574.09</v>
+      </c>
+      <c r="H86" s="1">
+        <v>1620.5</v>
+      </c>
+      <c r="I86" s="1">
+        <v>2438.32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C87" s="1">
         <v>640.03</v>
       </c>
       <c r="D87" s="1">
-        <v>730.35</v>
+        <v>730.3499999999999</v>
       </c>
       <c r="E87" s="1">
         <v>795.72</v>
@@ -2696,10 +3482,19 @@
       <c r="F87" s="1">
         <v>224.39</v>
       </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87" s="1">
+        <v>410.88</v>
+      </c>
+      <c r="H87" s="1">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I87" s="1">
+        <v>837.02</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C88" s="1">
         <v>324.33</v>
@@ -2713,16 +3508,25 @@
       <c r="F88" s="1">
         <v>318.95</v>
       </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88" s="1">
+        <v>134.97</v>
+      </c>
+      <c r="H88" s="1">
+        <v>271.95</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C89" s="1">
         <v>1166.91</v>
       </c>
       <c r="D89" s="1">
-        <v>575.86</v>
+        <v>692.85</v>
       </c>
       <c r="E89" s="1">
         <v>1470.73</v>
@@ -2730,27 +3534,45 @@
       <c r="F89" s="1">
         <v>1097.88</v>
       </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="G89" s="1">
+        <v>1512.95</v>
+      </c>
+      <c r="H89" s="1">
+        <v>1514.28</v>
+      </c>
+      <c r="I89" s="1">
+        <v>937.9100000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C90" s="1">
-        <v>2783.219999999999</v>
+        <v>2783.22</v>
       </c>
       <c r="D90" s="1">
         <v>2822.08</v>
       </c>
       <c r="E90" s="1">
-        <v>3843.18</v>
+        <v>3843.179999999999</v>
       </c>
       <c r="F90" s="1">
         <v>2733.76</v>
       </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="G90" s="1">
+        <v>2732.699999999999</v>
+      </c>
+      <c r="H90" s="1">
+        <v>3372.759999999999</v>
+      </c>
+      <c r="I90" s="1">
+        <v>3882.049999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C91" s="1">
         <v>1358.02</v>
@@ -2764,10 +3586,19 @@
       <c r="F91" s="1">
         <v>1513.13</v>
       </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="G91" s="1">
+        <v>1162.06</v>
+      </c>
+      <c r="H91" s="1">
+        <v>1555.84</v>
+      </c>
+      <c r="I91" s="1">
+        <v>1473.29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C92" s="1">
         <v>1410.62</v>
@@ -2781,10 +3612,19 @@
       <c r="F92" s="1">
         <v>1859.07</v>
       </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="G92" s="1">
+        <v>1057.07</v>
+      </c>
+      <c r="H92" s="1">
+        <v>2191.72</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1224.87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C93" s="1">
         <v>365.66</v>
@@ -2798,10 +3638,19 @@
       <c r="F93" s="1">
         <v>712.0599999999999</v>
       </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="G93" s="1">
+        <v>134.68</v>
+      </c>
+      <c r="H93" s="1">
+        <v>545.63</v>
+      </c>
+      <c r="I93" s="1">
+        <v>460.84</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C94" s="1">
         <v>2478.03</v>
@@ -2815,10 +3664,19 @@
       <c r="F94" s="1">
         <v>2300.71</v>
       </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="G94" s="1">
+        <v>2010.75</v>
+      </c>
+      <c r="H94" s="1">
+        <v>2207.09</v>
+      </c>
+      <c r="I94" s="1">
+        <v>3261.639999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C95" s="1">
         <v>1627.43</v>
@@ -2832,27 +3690,45 @@
       <c r="F95" s="1">
         <v>1809.04</v>
       </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="G95" s="1">
+        <v>1156.79</v>
+      </c>
+      <c r="H95" s="1">
+        <v>2953.01</v>
+      </c>
+      <c r="I95" s="1">
+        <v>1484.79</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C96" s="1">
-        <v>2378.149999999999</v>
+        <v>2378.15</v>
       </c>
       <c r="D96" s="1">
         <v>1614.56</v>
       </c>
       <c r="E96" s="1">
-        <v>2234.649999999999</v>
+        <v>2234.65</v>
       </c>
       <c r="F96" s="1">
-        <v>3000.949999999999</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>3000.95</v>
+      </c>
+      <c r="G96" s="1">
+        <v>2233.94</v>
+      </c>
+      <c r="H96" s="1">
+        <v>2074.8</v>
+      </c>
+      <c r="I96" s="1">
+        <v>2586.6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C97" s="1">
         <v>3255.669999999999</v>
@@ -2864,12 +3740,21 @@
         <v>3064.54</v>
       </c>
       <c r="F97" s="1">
-        <v>3185.59</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>3185.589999999999</v>
+      </c>
+      <c r="G97" s="1">
+        <v>2291.44</v>
+      </c>
+      <c r="H97" s="1">
+        <v>4246.619999999998</v>
+      </c>
+      <c r="I97" s="1">
+        <v>3770.599999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C98" s="1">
         <v>1761.87</v>
@@ -2883,10 +3768,19 @@
       <c r="F98" s="1">
         <v>1430.78</v>
       </c>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="G98" s="1">
+        <v>1852.35</v>
+      </c>
+      <c r="H98" s="1">
+        <v>1822.32</v>
+      </c>
+      <c r="I98" s="1">
+        <v>1673.83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C99" s="1">
         <v>387.95</v>
@@ -2900,10 +3794,19 @@
       <c r="F99" s="1">
         <v>880.71</v>
       </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="G99" s="1">
+        <v>1268.84</v>
+      </c>
+      <c r="H99" s="1">
+        <v>1000.87</v>
+      </c>
+      <c r="I99" s="1">
+        <v>634.83</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C100" s="1">
         <v>521.64</v>
@@ -2915,12 +3818,21 @@
         <v>980.9000000000001</v>
       </c>
       <c r="F100" s="1">
-        <v>732.22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>830.21</v>
+      </c>
+      <c r="G100" s="1">
+        <v>1050.24</v>
+      </c>
+      <c r="H100" s="1">
+        <v>738.8599999999999</v>
+      </c>
+      <c r="I100" s="1">
+        <v>638.1900000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C101" s="1">
         <v>1031.7</v>
@@ -2934,10 +3846,19 @@
       <c r="F101" s="1">
         <v>406.96</v>
       </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="G101" s="1">
+        <v>1419.31</v>
+      </c>
+      <c r="H101" s="1">
+        <v>839.47</v>
+      </c>
+      <c r="I101" s="1">
+        <v>795.52</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C102" s="1">
         <v>1865.01</v>
@@ -2951,10 +3872,19 @@
       <c r="F102" s="1">
         <v>1990.58</v>
       </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="G102" s="1">
+        <v>1391.05</v>
+      </c>
+      <c r="H102" s="1">
+        <v>2060.69</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1829.53</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C103" s="1">
         <v>1084.46</v>
@@ -2968,13 +3898,22 @@
       <c r="F103" s="1">
         <v>1556.92</v>
       </c>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="G103" s="1">
+        <v>1524.59</v>
+      </c>
+      <c r="H103" s="1">
+        <v>1830.06</v>
+      </c>
+      <c r="I103" s="1">
+        <v>2665.519999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C104" s="1">
-        <v>575.8299999999999</v>
+        <v>575.83</v>
       </c>
       <c r="D104" s="1">
         <v>495.93</v>
@@ -2985,10 +3924,19 @@
       <c r="F104" s="1">
         <v>528.74</v>
       </c>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="G104" s="1">
+        <v>397.3499999999999</v>
+      </c>
+      <c r="H104" s="1">
+        <v>522.11</v>
+      </c>
+      <c r="I104" s="1">
+        <v>901.95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C105" s="1">
         <v>1309.29</v>
@@ -3002,13 +3950,22 @@
       <c r="F105" s="1">
         <v>1000.85</v>
       </c>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="G105" s="1">
+        <v>410.84</v>
+      </c>
+      <c r="H105" s="1">
+        <v>618.54</v>
+      </c>
+      <c r="I105" s="1">
+        <v>945.6799999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C106" s="1">
-        <v>2465.679999999999</v>
+        <v>2465.68</v>
       </c>
       <c r="D106" s="1">
         <v>1239.24</v>
@@ -3019,10 +3976,19 @@
       <c r="F106" s="1">
         <v>2020.6</v>
       </c>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="G106" s="1">
+        <v>1407.49</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1440.05</v>
+      </c>
+      <c r="I106" s="1">
+        <v>1957.22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C107" s="1">
         <v>2030.19</v>
@@ -3036,16 +4002,25 @@
       <c r="F107" s="1">
         <v>1798.55</v>
       </c>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="G107" s="1">
+        <v>1786.12</v>
+      </c>
+      <c r="H107" s="1">
+        <v>2014.56</v>
+      </c>
+      <c r="I107" s="1">
+        <v>1769.04</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C108" s="1">
         <v>4506.059999999999</v>
       </c>
       <c r="D108" s="1">
-        <v>2671.499999999999</v>
+        <v>2671.5</v>
       </c>
       <c r="E108" s="1">
         <v>1755.66</v>
@@ -3053,16 +4028,25 @@
       <c r="F108" s="1">
         <v>2169.35</v>
       </c>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="G108" s="1">
+        <v>2208.84</v>
+      </c>
+      <c r="H108" s="1">
+        <v>3374.01</v>
+      </c>
+      <c r="I108" s="1">
+        <v>3224.54</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C109" s="1">
         <v>1359.96</v>
       </c>
       <c r="D109" s="1">
-        <v>606.53</v>
+        <v>606.5300000000001</v>
       </c>
       <c r="E109" s="1">
         <v>1192.87</v>
@@ -3070,13 +4054,22 @@
       <c r="F109" s="1">
         <v>1115.86</v>
       </c>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="G109" s="1">
+        <v>1089.06</v>
+      </c>
+      <c r="H109" s="1">
+        <v>1264.6</v>
+      </c>
+      <c r="I109" s="1">
+        <v>168.97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C110" s="1">
-        <v>872.61</v>
+        <v>872.6099999999999</v>
       </c>
       <c r="D110" s="1">
         <v>1093.74</v>
@@ -3087,10 +4080,19 @@
       <c r="F110" s="1">
         <v>916.6799999999999</v>
       </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="G110" s="1">
+        <v>583.98</v>
+      </c>
+      <c r="H110" s="1">
+        <v>699.89</v>
+      </c>
+      <c r="I110" s="1">
+        <v>663.75</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C111" s="1">
         <v>1055.85</v>
@@ -3104,10 +4106,19 @@
       <c r="F111" s="1">
         <v>1034.9</v>
       </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="G111" s="1">
+        <v>532.3100000000001</v>
+      </c>
+      <c r="H111" s="1">
+        <v>979.8200000000001</v>
+      </c>
+      <c r="I111" s="1">
+        <v>1144.03</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C112" s="1">
         <v>1788.69</v>
@@ -3121,16 +4132,25 @@
       <c r="F112" s="1">
         <v>1172.9</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" s="1">
+        <v>1097.09</v>
+      </c>
+      <c r="H112" s="1">
+        <v>2512.739999999999</v>
+      </c>
+      <c r="I112" s="1">
+        <v>766.91</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C113" s="1">
         <v>1646.6</v>
       </c>
       <c r="D113" s="1">
-        <v>2449.38</v>
+        <v>2449.379999999999</v>
       </c>
       <c r="E113" s="1">
         <v>1297.4</v>
@@ -3138,10 +4158,19 @@
       <c r="F113" s="1">
         <v>1743.85</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" s="1">
+        <v>1932.57</v>
+      </c>
+      <c r="H113" s="1">
+        <v>2229.59</v>
+      </c>
+      <c r="I113" s="1">
+        <v>1869.39</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C114" s="1">
         <v>776.73</v>
@@ -3155,16 +4184,25 @@
       <c r="F114" s="1">
         <v>624.9400000000001</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" s="1">
+        <v>347.64</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1126.48</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1229.72</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C115" s="1">
         <v>865.1900000000001</v>
       </c>
       <c r="D115" s="1">
-        <v>890.17</v>
+        <v>890.1700000000001</v>
       </c>
       <c r="E115" s="1">
         <v>1116.07</v>
@@ -3172,10 +4210,19 @@
       <c r="F115" s="1">
         <v>892.95</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" s="1">
+        <v>785.7199999999999</v>
+      </c>
+      <c r="H115" s="1">
+        <v>1204.19</v>
+      </c>
+      <c r="I115" s="1">
+        <v>1206.54</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C116" s="1">
         <v>1191.46</v>
@@ -3189,10 +4236,19 @@
       <c r="F116" s="1">
         <v>1584.19</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" s="1">
+        <v>1890.95</v>
+      </c>
+      <c r="H116" s="1">
+        <v>2078.2</v>
+      </c>
+      <c r="I116" s="1">
+        <v>2848.54</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C117" s="1">
         <v>1587</v>
@@ -3201,38 +4257,56 @@
         <v>430.7</v>
       </c>
       <c r="E117" s="1">
-        <v>817.9100000000001</v>
+        <v>817.91</v>
       </c>
       <c r="F117" s="1">
         <v>813.09</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" s="1">
+        <v>703.8099999999999</v>
+      </c>
+      <c r="H117" s="1">
+        <v>642.6</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C118" s="1">
-        <v>8642.889999999999</v>
+        <v>8642.889999999998</v>
       </c>
       <c r="D118" s="1">
-        <v>8980.849999999999</v>
+        <v>8980.850000000002</v>
       </c>
       <c r="E118" s="1">
-        <v>11185.23999999999</v>
+        <v>11185.24</v>
       </c>
       <c r="F118" s="1">
-        <v>7724.85</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>7724.849999999998</v>
+      </c>
+      <c r="G118" s="1">
+        <v>8220.189999999999</v>
+      </c>
+      <c r="H118" s="1">
+        <v>7258.75</v>
+      </c>
+      <c r="I118" s="1">
+        <v>7016.959999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C119" s="1">
         <v>1105.89</v>
       </c>
       <c r="D119" s="1">
-        <v>927.1600000000001</v>
+        <v>927.16</v>
       </c>
       <c r="E119" s="1">
         <v>1635.63</v>
@@ -3240,13 +4314,22 @@
       <c r="F119" s="1">
         <v>1019.38</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" s="1">
+        <v>648.0400000000001</v>
+      </c>
+      <c r="H119" s="1">
+        <v>1609.67</v>
+      </c>
+      <c r="I119" s="1">
+        <v>885.7800000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C120" s="1">
-        <v>3012.919999999999</v>
+        <v>3012.920000000001</v>
       </c>
       <c r="D120" s="1">
         <v>1019.76</v>
@@ -3257,16 +4340,25 @@
       <c r="F120" s="1">
         <v>2037.86</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" s="1">
+        <v>2304.24</v>
+      </c>
+      <c r="H120" s="1">
+        <v>3475.129999999999</v>
+      </c>
+      <c r="I120" s="1">
+        <v>2015.98</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C121" s="1">
         <v>969.74</v>
       </c>
       <c r="D121" s="1">
-        <v>524.95</v>
+        <v>524.9499999999999</v>
       </c>
       <c r="E121" s="1">
         <v>825.14</v>
@@ -3274,10 +4366,19 @@
       <c r="F121" s="1">
         <v>1237.25</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" s="1">
+        <v>669.53</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1300.05</v>
+      </c>
+      <c r="I121" s="1">
+        <v>627.03</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C122" s="1">
         <v>1249.05</v>
@@ -3291,13 +4392,22 @@
       <c r="F122" s="1">
         <v>1037.03</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" s="1">
+        <v>2287.55</v>
+      </c>
+      <c r="H122" s="1">
+        <v>2044.58</v>
+      </c>
+      <c r="I122" s="1">
+        <v>1600.38</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C123" s="1">
-        <v>720.62</v>
+        <v>720.6200000000001</v>
       </c>
       <c r="D123" s="1">
         <v>620.9400000000001</v>
@@ -3308,10 +4418,19 @@
       <c r="F123" s="1">
         <v>345.96</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" s="1">
+        <v>668.7</v>
+      </c>
+      <c r="H123" s="1">
+        <v>827.64</v>
+      </c>
+      <c r="I123" s="1">
+        <v>1250.71</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C124" s="1">
         <v>1168.83</v>
@@ -3325,10 +4444,19 @@
       <c r="F124" s="1">
         <v>937.49</v>
       </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="G124" s="1">
+        <v>569.92</v>
+      </c>
+      <c r="H124" s="1">
+        <v>1826.09</v>
+      </c>
+      <c r="I124" s="1">
+        <v>1042.91</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1">
         <v>929.7700000000001</v>
@@ -3342,10 +4470,19 @@
       <c r="F125" s="1">
         <v>1218.4</v>
       </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="G125" s="1">
+        <v>1346.88</v>
+      </c>
+      <c r="H125" s="1">
+        <v>1578.27</v>
+      </c>
+      <c r="I125" s="1">
+        <v>1919.75</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C126" s="1">
         <v>1015.34</v>
@@ -3359,27 +4496,45 @@
       <c r="F126" s="1">
         <v>863.9400000000001</v>
       </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="G126" s="1">
+        <v>1654.72</v>
+      </c>
+      <c r="H126" s="1">
+        <v>1423.75</v>
+      </c>
+      <c r="I126" s="1">
+        <v>1801.82</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C127" s="1">
-        <v>2404.39</v>
+        <v>2404.389999999999</v>
       </c>
       <c r="D127" s="1">
         <v>1227.05</v>
       </c>
       <c r="E127" s="1">
-        <v>837.5799999999999</v>
+        <v>837.58</v>
       </c>
       <c r="F127" s="1">
         <v>989.9400000000001</v>
       </c>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="G127" s="1">
+        <v>1018.32</v>
+      </c>
+      <c r="H127" s="1">
+        <v>1687.16</v>
+      </c>
+      <c r="I127" s="1">
+        <v>1643.72</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C128" s="1">
         <v>3053.78</v>
@@ -3393,27 +4548,45 @@
       <c r="F128" s="1">
         <v>3542.529999999999</v>
       </c>
-    </row>
-    <row r="129" spans="1:6">
+      <c r="G128" s="1">
+        <v>2356.579999999999</v>
+      </c>
+      <c r="H128" s="1">
+        <v>3937.29</v>
+      </c>
+      <c r="I128" s="1">
+        <v>3836.38</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C129" s="1">
-        <v>2726.469999999999</v>
+        <v>2726.47</v>
       </c>
       <c r="D129" s="1">
         <v>2247.33</v>
       </c>
       <c r="E129" s="1">
-        <v>1839.63</v>
+        <v>1928.62</v>
       </c>
       <c r="F129" s="1">
-        <v>3404.95</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>3404.949999999999</v>
+      </c>
+      <c r="G129" s="1">
+        <v>3873.47</v>
+      </c>
+      <c r="H129" s="1">
+        <v>2834.09</v>
+      </c>
+      <c r="I129" s="1">
+        <v>3362.04</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C130" s="1">
         <v>506.89</v>
@@ -3427,10 +4600,19 @@
       <c r="F130" s="1">
         <v>605.9400000000001</v>
       </c>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="G130" s="1">
+        <v>1217.81</v>
+      </c>
+      <c r="H130" s="1">
+        <v>869.8500000000001</v>
+      </c>
+      <c r="I130" s="1">
+        <v>812.83</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C131" s="1">
         <v>1163.82</v>
@@ -3444,10 +4626,19 @@
       <c r="F131" s="1">
         <v>313.94</v>
       </c>
-    </row>
-    <row r="132" spans="1:6">
+      <c r="G131" s="1">
+        <v>197.96</v>
+      </c>
+      <c r="H131" s="1">
+        <v>1515.78</v>
+      </c>
+      <c r="I131" s="1">
+        <v>563.91</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C132" s="1">
         <v>3173.72</v>
@@ -3459,15 +4650,24 @@
         <v>2934.97</v>
       </c>
       <c r="F132" s="1">
-        <v>5771.69</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>5771.689999999999</v>
+      </c>
+      <c r="G132" s="1">
+        <v>5374.42</v>
+      </c>
+      <c r="H132" s="1">
+        <v>3091.349999999999</v>
+      </c>
+      <c r="I132" s="1">
+        <v>3253.399999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C133" s="1">
-        <v>4722.56</v>
+        <v>4722.560000000001</v>
       </c>
       <c r="D133" s="1">
         <v>2918.52</v>
@@ -3478,10 +4678,19 @@
       <c r="F133" s="1">
         <v>2625.42</v>
       </c>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="G133" s="1">
+        <v>3626.96</v>
+      </c>
+      <c r="H133" s="1">
+        <v>3962.469999999999</v>
+      </c>
+      <c r="I133" s="1">
+        <v>5083.359999999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C134" s="1">
         <v>2125.16</v>
@@ -3495,13 +4704,22 @@
       <c r="F134" s="1">
         <v>2338.28</v>
       </c>
-    </row>
-    <row r="135" spans="1:6">
+      <c r="G134" s="1">
+        <v>2558.03</v>
+      </c>
+      <c r="H134" s="1">
+        <v>2257.97</v>
+      </c>
+      <c r="I134" s="1">
+        <v>2805.99</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C135" s="1">
-        <v>2397.92</v>
+        <v>2397.920000000001</v>
       </c>
       <c r="D135" s="1">
         <v>2150.4</v>
@@ -3512,10 +4730,19 @@
       <c r="F135" s="1">
         <v>2106.72</v>
       </c>
-    </row>
-    <row r="136" spans="1:6">
+      <c r="G135" s="1">
+        <v>2338.34</v>
+      </c>
+      <c r="H135" s="1">
+        <v>1655.81</v>
+      </c>
+      <c r="I135" s="1">
+        <v>3086.099999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C136" s="1">
         <v>593.8</v>
@@ -3529,10 +4756,19 @@
       <c r="F136" s="1">
         <v>343.76</v>
       </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="G136" s="1">
+        <v>1276.86</v>
+      </c>
+      <c r="H136" s="1">
+        <v>459.94</v>
+      </c>
+      <c r="I136" s="1">
+        <v>637.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C137" s="1">
         <v>1664.78</v>
@@ -3546,10 +4782,19 @@
       <c r="F137" s="1">
         <v>2202.62</v>
       </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" s="1">
+        <v>4147.06</v>
+      </c>
+      <c r="H137" s="1">
+        <v>3843.21</v>
+      </c>
+      <c r="I137" s="1">
+        <v>2656.539999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C138" s="1">
         <v>1809.95</v>
@@ -3563,10 +4808,19 @@
       <c r="F138" s="1">
         <v>1909.96</v>
       </c>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="G138" s="1">
+        <v>2513.53</v>
+      </c>
+      <c r="H138" s="1">
+        <v>2094.65</v>
+      </c>
+      <c r="I138" s="1">
+        <v>2203.18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C139" s="1">
         <v>1506.04</v>
@@ -3580,61 +4834,97 @@
       <c r="F139" s="1">
         <v>2382.12</v>
       </c>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="G139" s="1">
+        <v>1999.32</v>
+      </c>
+      <c r="H139" s="1">
+        <v>2871.92</v>
+      </c>
+      <c r="I139" s="1">
+        <v>1943.9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C140" s="1">
-        <v>6013.199999999997</v>
+        <v>6013.199999999999</v>
       </c>
       <c r="D140" s="1">
         <v>3724.859999999999</v>
       </c>
       <c r="E140" s="1">
-        <v>4590.549999999998</v>
+        <v>4590.549999999999</v>
       </c>
       <c r="F140" s="1">
-        <v>5382.139999999999</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+        <v>5382.139999999998</v>
+      </c>
+      <c r="G140" s="1">
+        <v>5103.029999999998</v>
+      </c>
+      <c r="H140" s="1">
+        <v>4766.919999999997</v>
+      </c>
+      <c r="I140" s="1">
+        <v>4181.999999999998</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C141" s="1">
         <v>1209.65</v>
       </c>
       <c r="D141" s="1">
-        <v>993.7200000000001</v>
+        <v>993.72</v>
       </c>
       <c r="E141" s="1">
         <v>1010.18</v>
       </c>
       <c r="F141" s="1">
-        <v>355.81</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+        <v>355.8099999999999</v>
+      </c>
+      <c r="G141" s="1">
+        <v>857.4200000000001</v>
+      </c>
+      <c r="H141" s="1">
+        <v>1105.69</v>
+      </c>
+      <c r="I141" s="1">
+        <v>708.38</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C142" s="1">
-        <v>2215.190000000001</v>
+        <v>2215.19</v>
       </c>
       <c r="D142" s="1">
         <v>1279.05</v>
       </c>
       <c r="E142" s="1">
-        <v>2533.909999999999</v>
+        <v>2533.91</v>
       </c>
       <c r="F142" s="1">
         <v>1719.43</v>
       </c>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" s="1">
+        <v>1661.94</v>
+      </c>
+      <c r="H142" s="1">
+        <v>1734.3</v>
+      </c>
+      <c r="I142" s="1">
+        <v>2101.69</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C143" s="1">
         <v>1040.97</v>
@@ -3648,10 +4938,19 @@
       <c r="F143" s="1">
         <v>1217.59</v>
       </c>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" s="1">
+        <v>1169.26</v>
+      </c>
+      <c r="H143" s="1">
+        <v>1329.01</v>
+      </c>
+      <c r="I143" s="1">
+        <v>717.9000000000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C144" s="1">
         <v>3560.509999999999</v>
@@ -3665,10 +4964,19 @@
       <c r="F144" s="1">
         <v>2424.57</v>
       </c>
-    </row>
-    <row r="145" spans="1:6">
+      <c r="G144" s="1">
+        <v>2475.36</v>
+      </c>
+      <c r="H144" s="1">
+        <v>3136.119999999999</v>
+      </c>
+      <c r="I144" s="1">
+        <v>2164.79</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C145" s="1">
         <v>969.09</v>
@@ -3682,16 +4990,25 @@
       <c r="F145" s="1">
         <v>991.4400000000001</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="G145" s="1">
+        <v>792.11</v>
+      </c>
+      <c r="H145" s="1">
+        <v>799.6400000000001</v>
+      </c>
+      <c r="I145" s="1">
+        <v>532.9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C146" s="1">
-        <v>892.3400000000001</v>
+        <v>892.34</v>
       </c>
       <c r="D146" s="1">
-        <v>583.63</v>
+        <v>583.6299999999999</v>
       </c>
       <c r="E146" s="1">
         <v>708.23</v>
@@ -3699,10 +5016,19 @@
       <c r="F146" s="1">
         <v>551.9299999999999</v>
       </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" s="1">
+        <v>478.89</v>
+      </c>
+      <c r="H146" s="1">
+        <v>1051.13</v>
+      </c>
+      <c r="I146" s="1">
+        <v>1597.11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C147" s="1">
         <v>1586.36</v>
@@ -3716,10 +5042,19 @@
       <c r="F147" s="1">
         <v>1012.31</v>
       </c>
-    </row>
-    <row r="148" spans="1:6">
+      <c r="G147" s="1">
+        <v>696.8</v>
+      </c>
+      <c r="H147" s="1">
+        <v>981.6900000000001</v>
+      </c>
+      <c r="I147" s="1">
+        <v>793.65</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C148" s="1">
         <v>1371.21</v>
@@ -3733,16 +5068,25 @@
       <c r="F148" s="1">
         <v>1927.94</v>
       </c>
-    </row>
-    <row r="149" spans="1:6">
+      <c r="G148" s="1">
+        <v>1735.1</v>
+      </c>
+      <c r="H148" s="1">
+        <v>2080.89</v>
+      </c>
+      <c r="I148" s="1">
+        <v>2385.1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C149" s="1">
-        <v>3889.549999999999</v>
+        <v>3889.550000000001</v>
       </c>
       <c r="D149" s="1">
-        <v>3416.799999999999</v>
+        <v>3416.8</v>
       </c>
       <c r="E149" s="1">
         <v>2429.53</v>
@@ -3750,10 +5094,19 @@
       <c r="F149" s="1">
         <v>1993.79</v>
       </c>
-    </row>
-    <row r="150" spans="1:6">
+      <c r="G149" s="1">
+        <v>3913.399999999999</v>
+      </c>
+      <c r="H149" s="1">
+        <v>5258.359999999998</v>
+      </c>
+      <c r="I149" s="1">
+        <v>4063.429999999999</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C150" s="1">
         <v>190.96</v>
@@ -3767,13 +5120,22 @@
       <c r="F150" s="1">
         <v>542.92</v>
       </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="G150" s="1">
+        <v>359.95</v>
+      </c>
+      <c r="H150" s="1">
+        <v>250.95</v>
+      </c>
+      <c r="I150" s="1">
+        <v>1140.82</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C151" s="1">
-        <v>4129.599999999999</v>
+        <v>4129.6</v>
       </c>
       <c r="D151" s="1">
         <v>4484.059999999999</v>
@@ -3784,10 +5146,19 @@
       <c r="F151" s="1">
         <v>2474.23</v>
       </c>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="G151" s="1">
+        <v>3620.299999999999</v>
+      </c>
+      <c r="H151" s="1">
+        <v>2786.809999999999</v>
+      </c>
+      <c r="I151" s="1">
+        <v>1978.29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C152" s="1">
         <v>1587.06</v>
@@ -3799,12 +5170,21 @@
         <v>2164.44</v>
       </c>
       <c r="F152" s="1">
-        <v>985.2900000000001</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
+        <v>985.29</v>
+      </c>
+      <c r="G152" s="1">
+        <v>1383.41</v>
+      </c>
+      <c r="H152" s="1">
+        <v>1013.89</v>
+      </c>
+      <c r="I152" s="1">
+        <v>2600.49</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C153" s="1">
         <v>1066.01</v>
@@ -3818,10 +5198,19 @@
       <c r="F153" s="1">
         <v>1375.59</v>
       </c>
-    </row>
-    <row r="154" spans="1:6">
+      <c r="G153" s="1">
+        <v>1394.5</v>
+      </c>
+      <c r="H153" s="1">
+        <v>1884.06</v>
+      </c>
+      <c r="I153" s="1">
+        <v>1905.92</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C154" s="1">
         <v>2176.35</v>
@@ -3835,16 +5224,25 @@
       <c r="F154" s="1">
         <v>2049.93</v>
       </c>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="G154" s="1">
+        <v>1700.3</v>
+      </c>
+      <c r="H154" s="1">
+        <v>3273.21</v>
+      </c>
+      <c r="I154" s="1">
+        <v>2944.469999999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C155" s="1">
-        <v>4112.26</v>
+        <v>4112.259999999999</v>
       </c>
       <c r="D155" s="1">
-        <v>4357.42</v>
+        <v>4357.419999999998</v>
       </c>
       <c r="E155" s="1">
         <v>4745.269999999999</v>
@@ -3852,13 +5250,22 @@
       <c r="F155" s="1">
         <v>3493.25</v>
       </c>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="G155" s="1">
+        <v>5195.009999999999</v>
+      </c>
+      <c r="H155" s="1">
+        <v>3973.95</v>
+      </c>
+      <c r="I155" s="1">
+        <v>2686.4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C156" s="1">
-        <v>3383.850000000001</v>
+        <v>3383.849999999999</v>
       </c>
       <c r="D156" s="1">
         <v>2040.14</v>
@@ -3869,10 +5276,19 @@
       <c r="F156" s="1">
         <v>2741.78</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="G156" s="1">
+        <v>3475.889999999999</v>
+      </c>
+      <c r="H156" s="1">
+        <v>3780.109999999999</v>
+      </c>
+      <c r="I156" s="1">
+        <v>4776.110000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C157" s="1">
         <v>3609.78</v>
@@ -3884,29 +5300,47 @@
         <v>6408.18</v>
       </c>
       <c r="F157" s="1">
-        <v>4894.419999999998</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
+        <v>4894.419999999999</v>
+      </c>
+      <c r="G157" s="1">
+        <v>3947.79</v>
+      </c>
+      <c r="H157" s="1">
+        <v>5208.61</v>
+      </c>
+      <c r="I157" s="1">
+        <v>3634.16</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C158" s="1">
-        <v>2702.669999999999</v>
+        <v>2702.67</v>
       </c>
       <c r="D158" s="1">
-        <v>3182.679999999999</v>
+        <v>3182.68</v>
       </c>
       <c r="E158" s="1">
         <v>2169.64</v>
       </c>
       <c r="F158" s="1">
-        <v>2464.299999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
+        <v>2464.3</v>
+      </c>
+      <c r="G158" s="1">
+        <v>2315.59</v>
+      </c>
+      <c r="H158" s="1">
+        <v>1370.43</v>
+      </c>
+      <c r="I158" s="1">
+        <v>1920.33</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C159" s="1">
         <v>1934.42</v>
@@ -3920,10 +5354,19 @@
       <c r="F159" s="1">
         <v>1619.53</v>
       </c>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="G159" s="1">
+        <v>2739.15</v>
+      </c>
+      <c r="H159" s="1">
+        <v>1537.96</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C160" s="1">
         <v>1131.05</v>
@@ -3932,38 +5375,56 @@
         <v>1578.85</v>
       </c>
       <c r="E160" s="1">
-        <v>615.9200000000001</v>
+        <v>615.92</v>
       </c>
       <c r="F160" s="1">
         <v>990.39</v>
       </c>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="G160" s="1">
+        <v>957.91</v>
+      </c>
+      <c r="H160" s="1">
+        <v>1544.44</v>
+      </c>
+      <c r="I160" s="1">
+        <v>1031.2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C161" s="1">
         <v>3440.079999999999</v>
       </c>
       <c r="D161" s="1">
-        <v>4128.8</v>
+        <v>4128.799999999999</v>
       </c>
       <c r="E161" s="1">
         <v>1901.17</v>
       </c>
       <c r="F161" s="1">
-        <v>3113.01</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+        <v>3137</v>
+      </c>
+      <c r="G161" s="1">
+        <v>3096.860000000001</v>
+      </c>
+      <c r="H161" s="1">
+        <v>3026.329999999999</v>
+      </c>
+      <c r="I161" s="1">
+        <v>3015.509999999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C162" s="1">
         <v>1021.53</v>
       </c>
       <c r="D162" s="1">
-        <v>654.6300000000001</v>
+        <v>654.63</v>
       </c>
       <c r="E162" s="1">
         <v>692.08</v>
@@ -3971,10 +5432,19 @@
       <c r="F162" s="1">
         <v>812.6900000000001</v>
       </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="G162" s="1">
+        <v>480.6799999999999</v>
+      </c>
+      <c r="H162" s="1">
+        <v>1213.79</v>
+      </c>
+      <c r="I162" s="1">
+        <v>786.09</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C163" s="1">
         <v>844.29</v>
@@ -3988,10 +5458,19 @@
       <c r="F163" s="1">
         <v>811.11</v>
       </c>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="G163" s="1">
+        <v>2670.44</v>
+      </c>
+      <c r="H163" s="1">
+        <v>1445.52</v>
+      </c>
+      <c r="I163" s="1">
+        <v>2852.669999999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C164" s="1">
         <v>1013.8</v>
@@ -4005,13 +5484,22 @@
       <c r="F164" s="1">
         <v>824.9200000000001</v>
       </c>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="G164" s="1">
+        <v>437.84</v>
+      </c>
+      <c r="H164" s="1">
+        <v>767</v>
+      </c>
+      <c r="I164" s="1">
+        <v>1347.78</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C165" s="1">
-        <v>809.29</v>
+        <v>809.2900000000001</v>
       </c>
       <c r="D165" s="1">
         <v>2317.13</v>
@@ -4022,10 +5510,19 @@
       <c r="F165" s="1">
         <v>2320.86</v>
       </c>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="G165" s="1">
+        <v>1522.56</v>
+      </c>
+      <c r="H165" s="1">
+        <v>1352.32</v>
+      </c>
+      <c r="I165" s="1">
+        <v>1505.46</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C166" s="1">
         <v>814.74</v>
@@ -4039,27 +5536,45 @@
       <c r="F166" s="1">
         <v>974.9000000000001</v>
       </c>
-    </row>
-    <row r="167" spans="1:6">
+      <c r="G166" s="1">
+        <v>1664.56</v>
+      </c>
+      <c r="H166" s="1">
+        <v>1059.31</v>
+      </c>
+      <c r="I166" s="1">
+        <v>802.6799999999999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C167" s="1">
-        <v>8243.559999999999</v>
+        <v>8243.560000000001</v>
       </c>
       <c r="D167" s="1">
-        <v>7284.07</v>
+        <v>7284.069999999999</v>
       </c>
       <c r="E167" s="1">
-        <v>8566.989999999998</v>
+        <v>8566.99</v>
       </c>
       <c r="F167" s="1">
         <v>8110.14</v>
       </c>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="G167" s="1">
+        <v>7111.879999999998</v>
+      </c>
+      <c r="H167" s="1">
+        <v>8072.659999999996</v>
+      </c>
+      <c r="I167" s="1">
+        <v>6970.129999999998</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C168" s="1">
         <v>146.13</v>
@@ -4073,27 +5588,45 @@
       <c r="F168" s="1">
         <v>158.37</v>
       </c>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="G168" s="1">
+        <v>202.47</v>
+      </c>
+      <c r="H168" s="1">
+        <v>593.12</v>
+      </c>
+      <c r="I168" s="1">
+        <v>186.13</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C169" s="1">
-        <v>2854.749999999999</v>
+        <v>2854.75</v>
       </c>
       <c r="D169" s="1">
-        <v>2757.38</v>
+        <v>2757.379999999999</v>
       </c>
       <c r="E169" s="1">
         <v>3194.09</v>
       </c>
       <c r="F169" s="1">
-        <v>2583.77</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
+        <v>2676.759999999999</v>
+      </c>
+      <c r="G169" s="1">
+        <v>3984.5</v>
+      </c>
+      <c r="H169" s="1">
+        <v>3243.73</v>
+      </c>
+      <c r="I169" s="1">
+        <v>4045.759999999998</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C170" s="1">
         <v>716.29</v>
@@ -4107,16 +5640,25 @@
       <c r="F170" s="1">
         <v>995.0300000000001</v>
       </c>
-    </row>
-    <row r="171" spans="1:6">
+      <c r="G170" s="1">
+        <v>328.88</v>
+      </c>
+      <c r="H170" s="1">
+        <v>320.96</v>
+      </c>
+      <c r="I170" s="1">
+        <v>248.16</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C171" s="1">
         <v>688.29</v>
       </c>
       <c r="D171" s="1">
-        <v>532.85</v>
+        <v>532.8499999999999</v>
       </c>
       <c r="E171" s="1">
         <v>1001.4</v>
@@ -4124,13 +5666,22 @@
       <c r="F171" s="1">
         <v>913.21</v>
       </c>
-    </row>
-    <row r="172" spans="1:6">
+      <c r="G171" s="1">
+        <v>1009.65</v>
+      </c>
+      <c r="H171" s="1">
+        <v>1101.65</v>
+      </c>
+      <c r="I171" s="1">
+        <v>1070.51</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C172" s="1">
-        <v>2654.46</v>
+        <v>2654.459999999999</v>
       </c>
       <c r="D172" s="1">
         <v>2205.87</v>
@@ -4139,12 +5690,21 @@
         <v>3020.379999999999</v>
       </c>
       <c r="F172" s="1">
-        <v>2050.66</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
+        <v>2210.65</v>
+      </c>
+      <c r="G172" s="1">
+        <v>3061.06</v>
+      </c>
+      <c r="H172" s="1">
+        <v>3481.71</v>
+      </c>
+      <c r="I172" s="1">
+        <v>3779.829999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C173" s="1">
         <v>605.6799999999999</v>
@@ -4158,33 +5718,51 @@
       <c r="F173" s="1">
         <v>2286.86</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
+      <c r="G173" s="1">
+        <v>1465.14</v>
+      </c>
+      <c r="H173" s="1">
+        <v>2571.19</v>
+      </c>
+      <c r="I173" s="1">
+        <v>2423.58</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C174" s="1">
         <v>1205.25</v>
       </c>
       <c r="D174" s="1">
-        <v>2428.29</v>
+        <v>2428.289999999999</v>
       </c>
       <c r="E174" s="1">
-        <v>2788.029999999999</v>
+        <v>2788.03</v>
       </c>
       <c r="F174" s="1">
         <v>1898.72</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
+      <c r="G174" s="1">
+        <v>2317.76</v>
+      </c>
+      <c r="H174" s="1">
+        <v>2054.78</v>
+      </c>
+      <c r="I174" s="1">
+        <v>2015.89</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C175" s="1">
-        <v>2340.719999999999</v>
+        <v>2340.72</v>
       </c>
       <c r="D175" s="1">
-        <v>3721.649999999999</v>
+        <v>3721.650000000001</v>
       </c>
       <c r="E175" s="1">
         <v>1733.08</v>
@@ -4192,13 +5770,22 @@
       <c r="F175" s="1">
         <v>2413.25</v>
       </c>
-    </row>
-    <row r="176" spans="1:6">
+      <c r="G175" s="1">
+        <v>4977.24</v>
+      </c>
+      <c r="H175" s="1">
+        <v>2003.79</v>
+      </c>
+      <c r="I175" s="1">
+        <v>2708.26</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C176" s="1">
-        <v>2486.369999999999</v>
+        <v>2486.37</v>
       </c>
       <c r="D176" s="1">
         <v>1845.31</v>
@@ -4209,13 +5796,22 @@
       <c r="F176" s="1">
         <v>1367.77</v>
       </c>
-    </row>
-    <row r="177" spans="1:6">
+      <c r="G176" s="1">
+        <v>797.7900000000001</v>
+      </c>
+      <c r="H176" s="1">
+        <v>1826.26</v>
+      </c>
+      <c r="I176" s="1">
+        <v>1349.59</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C177" s="1">
-        <v>2185.940000000001</v>
+        <v>2185.94</v>
       </c>
       <c r="D177" s="1">
         <v>1577.41</v>
@@ -4226,10 +5822,19 @@
       <c r="F177" s="1">
         <v>1095.98</v>
       </c>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="G177" s="1">
+        <v>1548.03</v>
+      </c>
+      <c r="H177" s="1">
+        <v>2310.06</v>
+      </c>
+      <c r="I177" s="1">
+        <v>1010.69</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C178" s="1">
         <v>1210.03</v>
@@ -4243,13 +5848,22 @@
       <c r="F178" s="1">
         <v>1850.96</v>
       </c>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="G178" s="1">
+        <v>1360.43</v>
+      </c>
+      <c r="H178" s="1">
+        <v>1367.37</v>
+      </c>
+      <c r="I178" s="1">
+        <v>1554.37</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="D179" s="1">
         <v>480.91</v>
@@ -4260,10 +5874,19 @@
       <c r="F179" s="1">
         <v>188.96</v>
       </c>
-    </row>
-    <row r="180" spans="1:6">
+      <c r="G179" s="1">
+        <v>308.94</v>
+      </c>
+      <c r="H179" s="1">
+        <v>571.6900000000001</v>
+      </c>
+      <c r="I179" s="1">
+        <v>306.94</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C180" s="1">
         <v>1442.97</v>
@@ -4277,10 +5900,19 @@
       <c r="F180" s="1">
         <v>2241.96</v>
       </c>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="G180" s="1">
+        <v>1288.96</v>
+      </c>
+      <c r="H180" s="1">
+        <v>1179.83</v>
+      </c>
+      <c r="I180" s="1">
+        <v>1491.72</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C181" s="1">
         <v>736.0700000000001</v>
@@ -4294,10 +5926,19 @@
       <c r="F181" s="1">
         <v>1096.03</v>
       </c>
-    </row>
-    <row r="182" spans="1:6">
+      <c r="G181" s="1">
+        <v>934.65</v>
+      </c>
+      <c r="H181" s="1">
+        <v>1286.36</v>
+      </c>
+      <c r="I181" s="1">
+        <v>541.27</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C182" s="1">
         <v>700.62</v>
@@ -4309,12 +5950,21 @@
         <v>577.3200000000001</v>
       </c>
       <c r="F182" s="1">
-        <v>913.0200000000001</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
+        <v>913.02</v>
+      </c>
+      <c r="G182" s="1">
+        <v>830.61</v>
+      </c>
+      <c r="H182" s="1">
+        <v>878.0500000000002</v>
+      </c>
+      <c r="I182" s="1">
+        <v>345.49</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C183" s="1">
         <v>2037.33</v>
@@ -4328,10 +5978,19 @@
       <c r="F183" s="1">
         <v>2725.95</v>
       </c>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="G183" s="1">
+        <v>1350.39</v>
+      </c>
+      <c r="H183" s="1">
+        <v>1497.05</v>
+      </c>
+      <c r="I183" s="1">
+        <v>1719.58</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C184" s="1">
         <v>1870.07</v>
@@ -4345,16 +6004,25 @@
       <c r="F184" s="1">
         <v>1160.17</v>
       </c>
-    </row>
-    <row r="185" spans="1:6">
+      <c r="G184" s="1">
+        <v>1440.22</v>
+      </c>
+      <c r="H184" s="1">
+        <v>1290.95</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C185" s="1">
-        <v>2560.26</v>
+        <v>2560.259999999999</v>
       </c>
       <c r="D185" s="1">
-        <v>3008.319999999999</v>
+        <v>3008.32</v>
       </c>
       <c r="E185" s="1">
         <v>6660.709999999999</v>
@@ -4362,16 +6030,25 @@
       <c r="F185" s="1">
         <v>4120.179999999999</v>
       </c>
-    </row>
-    <row r="186" spans="1:6">
+      <c r="G185" s="1">
+        <v>3695.75</v>
+      </c>
+      <c r="H185" s="1">
+        <v>4141.699999999999</v>
+      </c>
+      <c r="I185" s="1">
+        <v>5456.769999999999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C186" s="1">
         <v>2387.07</v>
       </c>
       <c r="D186" s="1">
-        <v>3439.05</v>
+        <v>3439.049999999999</v>
       </c>
       <c r="E186" s="1">
         <v>3193.849999999999</v>
@@ -4379,10 +6056,19 @@
       <c r="F186" s="1">
         <v>2618.18</v>
       </c>
-    </row>
-    <row r="187" spans="1:6">
+      <c r="G186" s="1">
+        <v>2589.41</v>
+      </c>
+      <c r="H186" s="1">
+        <v>2829.87</v>
+      </c>
+      <c r="I186" s="1">
+        <v>3435.35</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C187" s="1">
         <v>1245.6</v>
@@ -4391,32 +6077,50 @@
         <v>338.22</v>
       </c>
       <c r="E187" s="1">
-        <v>507.4299999999999</v>
+        <v>507.43</v>
       </c>
       <c r="F187" s="1">
         <v>962.28</v>
       </c>
-    </row>
-    <row r="188" spans="1:6">
+      <c r="G187" s="1">
+        <v>506.42</v>
+      </c>
+      <c r="H187" s="1">
+        <v>389.79</v>
+      </c>
+      <c r="I187" s="1">
+        <v>799.36</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C188" s="1">
         <v>3493.439999999999</v>
       </c>
       <c r="D188" s="1">
-        <v>4656.55</v>
+        <v>4656.549999999999</v>
       </c>
       <c r="E188" s="1">
-        <v>2699.689999999999</v>
+        <v>2699.69</v>
       </c>
       <c r="F188" s="1">
-        <v>2598.109999999999</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
+        <v>2598.11</v>
+      </c>
+      <c r="G188" s="1">
+        <v>3305.46</v>
+      </c>
+      <c r="H188" s="1">
+        <v>3955.489999999999</v>
+      </c>
+      <c r="I188" s="1">
+        <v>2323.54</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C189" s="1">
         <v>3633.439999999999</v>
@@ -4430,10 +6134,19 @@
       <c r="F189" s="1">
         <v>3981.35</v>
       </c>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="G189" s="1">
+        <v>3049.52</v>
+      </c>
+      <c r="H189" s="1">
+        <v>3270.29</v>
+      </c>
+      <c r="I189" s="1">
+        <v>2035.36</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C190" s="1">
         <v>576.9299999999999</v>
@@ -4447,10 +6160,19 @@
       <c r="F190" s="1">
         <v>616.35</v>
       </c>
-    </row>
-    <row r="191" spans="1:6">
+      <c r="G190" s="1">
+        <v>458.33</v>
+      </c>
+      <c r="H190" s="1">
+        <v>1486.95</v>
+      </c>
+      <c r="I190" s="1">
+        <v>684.9100000000001</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C191" s="1">
         <v>777.66</v>
@@ -4464,10 +6186,19 @@
       <c r="F191" s="1">
         <v>390.56</v>
       </c>
-    </row>
-    <row r="192" spans="1:6">
+      <c r="G191" s="1">
+        <v>403.9000000000001</v>
+      </c>
+      <c r="H191" s="1">
+        <v>1057.22</v>
+      </c>
+      <c r="I191" s="1">
+        <v>277.86</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C192" s="1">
         <v>825.83</v>
@@ -4476,15 +6207,24 @@
         <v>1196.97</v>
       </c>
       <c r="E192" s="1">
-        <v>582.45</v>
+        <v>582.4499999999998</v>
       </c>
       <c r="F192" s="1">
         <v>671.8</v>
       </c>
-    </row>
-    <row r="193" spans="1:6">
+      <c r="G192" s="1">
+        <v>900.59</v>
+      </c>
+      <c r="H192" s="1">
+        <v>1107.13</v>
+      </c>
+      <c r="I192" s="1">
+        <v>476.79</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C193" s="1">
         <v>2030.98</v>
@@ -4496,12 +6236,21 @@
         <v>1344.77</v>
       </c>
       <c r="F193" s="1">
-        <v>2419.219999999999</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
+        <v>2419.22</v>
+      </c>
+      <c r="G193" s="1">
+        <v>1353.83</v>
+      </c>
+      <c r="H193" s="1">
+        <v>3023.73</v>
+      </c>
+      <c r="I193" s="1">
+        <v>2609.689999999999</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C194" s="1">
         <v>4686.129999999999</v>
@@ -4510,32 +6259,50 @@
         <v>4875.17</v>
       </c>
       <c r="E194" s="1">
-        <v>2466.520000000001</v>
+        <v>2466.52</v>
       </c>
       <c r="F194" s="1">
-        <v>4592.569999999999</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
+        <v>4592.57</v>
+      </c>
+      <c r="G194" s="1">
+        <v>4341.279999999998</v>
+      </c>
+      <c r="H194" s="1">
+        <v>3387.969999999999</v>
+      </c>
+      <c r="I194" s="1">
+        <v>3211.769999999999</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C195" s="1">
         <v>2149.42</v>
       </c>
       <c r="D195" s="1">
-        <v>4165.860000000001</v>
+        <v>4165.86</v>
       </c>
       <c r="E195" s="1">
-        <v>2985.829999999999</v>
+        <v>2985.83</v>
       </c>
       <c r="F195" s="1">
         <v>3367.170000000001</v>
       </c>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" s="1">
+        <v>4589.599999999999</v>
+      </c>
+      <c r="H195" s="1">
+        <v>3442.8</v>
+      </c>
+      <c r="I195" s="1">
+        <v>3963.279999999999</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C196" s="1">
         <v>1377.26</v>
@@ -4547,12 +6314,21 @@
         <v>903.9299999999999</v>
       </c>
       <c r="F196" s="1">
-        <v>871.4499999999998</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
+        <v>871.45</v>
+      </c>
+      <c r="G196" s="1">
+        <v>813.04</v>
+      </c>
+      <c r="H196" s="1">
+        <v>1815.23</v>
+      </c>
+      <c r="I196" s="1">
+        <v>2236.63</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C197" s="1">
         <v>2127.53</v>
@@ -4566,10 +6342,19 @@
       <c r="F197" s="1">
         <v>2626.39</v>
       </c>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G197" s="1">
+        <v>2981.22</v>
+      </c>
+      <c r="H197" s="1">
+        <v>2249.45</v>
+      </c>
+      <c r="I197" s="1">
+        <v>1876.65</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C198" s="1">
         <v>2559.889999999999</v>
@@ -4583,10 +6368,19 @@
       <c r="F198" s="1">
         <v>2364.44</v>
       </c>
-    </row>
-    <row r="199" spans="1:6">
+      <c r="G198" s="1">
+        <v>2919.79</v>
+      </c>
+      <c r="H198" s="1">
+        <v>3715.5</v>
+      </c>
+      <c r="I198" s="1">
+        <v>4012.979999999999</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C199" s="1">
         <v>1151.2</v>
@@ -4600,16 +6394,25 @@
       <c r="F199" s="1">
         <v>823.64</v>
       </c>
-    </row>
-    <row r="200" spans="1:6">
+      <c r="G199" s="1">
+        <v>647.6900000000001</v>
+      </c>
+      <c r="H199" s="1">
+        <v>946.85</v>
+      </c>
+      <c r="I199" s="1">
+        <v>568.9100000000001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C200" s="1">
-        <v>736.45</v>
+        <v>736.4499999999998</v>
       </c>
       <c r="D200" s="1">
-        <v>348.94</v>
+        <v>348.9399999999999</v>
       </c>
       <c r="E200" s="1">
         <v>998.0599999999999</v>
@@ -4617,27 +6420,45 @@
       <c r="F200" s="1">
         <v>1106.36</v>
       </c>
-    </row>
-    <row r="201" spans="1:6">
+      <c r="G200" s="1">
+        <v>763.9</v>
+      </c>
+      <c r="H200" s="1">
+        <v>1331.11</v>
+      </c>
+      <c r="I200" s="1">
+        <v>820.9</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C201" s="1">
-        <v>8280.029999999999</v>
+        <v>8280.030000000001</v>
       </c>
       <c r="D201" s="1">
-        <v>4925.719999999999</v>
+        <v>4925.719999999998</v>
       </c>
       <c r="E201" s="1">
         <v>5830.599999999999</v>
       </c>
       <c r="F201" s="1">
-        <v>8590.639999999998</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
+        <v>8678.629999999999</v>
+      </c>
+      <c r="G201" s="1">
+        <v>6083.81</v>
+      </c>
+      <c r="H201" s="1">
+        <v>10265.99</v>
+      </c>
+      <c r="I201" s="1">
+        <v>11471.1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C202" s="1">
         <v>1232.38</v>
@@ -4646,15 +6467,24 @@
         <v>901.33</v>
       </c>
       <c r="E202" s="1">
-        <v>573.1199999999999</v>
+        <v>573.12</v>
       </c>
       <c r="F202" s="1">
         <v>1544.36</v>
       </c>
-    </row>
-    <row r="203" spans="1:6">
+      <c r="G202" s="1">
+        <v>792.0100000000001</v>
+      </c>
+      <c r="H202" s="1">
+        <v>2615.61</v>
+      </c>
+      <c r="I202" s="1">
+        <v>1894.62</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C203" s="1">
         <v>1230.6</v>
@@ -4668,13 +6498,22 @@
       <c r="F203" s="1">
         <v>777.8</v>
       </c>
-    </row>
-    <row r="204" spans="1:6">
+      <c r="G203" s="1">
+        <v>1315.58</v>
+      </c>
+      <c r="H203" s="1">
+        <v>1553.2</v>
+      </c>
+      <c r="I203" s="1">
+        <v>512.9400000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C204" s="1">
-        <v>420.3499999999999</v>
+        <v>420.35</v>
       </c>
       <c r="D204" s="1">
         <v>281.97</v>
@@ -4685,10 +6524,19 @@
       <c r="F204" s="1">
         <v>508.77</v>
       </c>
-    </row>
-    <row r="205" spans="1:6">
+      <c r="G204" s="1">
+        <v>786.83</v>
+      </c>
+      <c r="H204" s="1">
+        <v>1329.86</v>
+      </c>
+      <c r="I204" s="1">
+        <v>365.97</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C205" s="1">
         <v>2571.28</v>
@@ -4702,10 +6550,19 @@
       <c r="F205" s="1">
         <v>1851.68</v>
       </c>
-    </row>
-    <row r="206" spans="1:6">
+      <c r="G205" s="1">
+        <v>2580.46</v>
+      </c>
+      <c r="H205" s="1">
+        <v>2442.52</v>
+      </c>
+      <c r="I205" s="1">
+        <v>1857.03</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C206" s="1">
         <v>1390.03</v>
@@ -4714,18 +6571,27 @@
         <v>1896.56</v>
       </c>
       <c r="E206" s="1">
-        <v>642.5300000000001</v>
+        <v>642.53</v>
       </c>
       <c r="F206" s="1">
         <v>940.4400000000001</v>
       </c>
-    </row>
-    <row r="207" spans="1:6">
+      <c r="G206" s="1">
+        <v>587.6</v>
+      </c>
+      <c r="H206" s="1">
+        <v>2245.02</v>
+      </c>
+      <c r="I206" s="1">
+        <v>1732.29</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C207" s="1">
-        <v>496.92</v>
+        <v>496.9200000000001</v>
       </c>
       <c r="D207" s="1">
         <v>978.8900000000001</v>
@@ -4736,10 +6602,19 @@
       <c r="F207" s="1">
         <v>1509.32</v>
       </c>
-    </row>
-    <row r="208" spans="1:6">
+      <c r="G207" s="1">
+        <v>480.92</v>
+      </c>
+      <c r="H207" s="1">
+        <v>638.8800000000001</v>
+      </c>
+      <c r="I207" s="1">
+        <v>857.7600000000001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C208" s="1">
         <v>2158.29</v>
@@ -4753,10 +6628,19 @@
       <c r="F208" s="1">
         <v>1398.06</v>
       </c>
-    </row>
-    <row r="209" spans="1:6">
+      <c r="G208" s="1">
+        <v>2286.09</v>
+      </c>
+      <c r="H208" s="1">
+        <v>2611.59</v>
+      </c>
+      <c r="I208" s="1">
+        <v>1691.24</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C209" s="1">
         <v>439.95</v>
@@ -4770,10 +6654,19 @@
       <c r="F209" s="1">
         <v>707.38</v>
       </c>
-    </row>
-    <row r="210" spans="1:6">
+      <c r="G209" s="1">
+        <v>1044.74</v>
+      </c>
+      <c r="H209" s="1">
+        <v>1255.82</v>
+      </c>
+      <c r="I209" s="1">
+        <v>808.8900000000001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C210" s="1">
         <v>1577.95</v>
@@ -4787,10 +6680,19 @@
       <c r="F210" s="1">
         <v>479.31</v>
       </c>
-    </row>
-    <row r="211" spans="1:6">
+      <c r="G210" s="1">
+        <v>1393.7</v>
+      </c>
+      <c r="H210" s="1">
+        <v>1894.05</v>
+      </c>
+      <c r="I210" s="1">
+        <v>1175.09</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C211" s="1">
         <v>1001.6</v>
@@ -4804,10 +6706,19 @@
       <c r="F211" s="1">
         <v>522.9400000000001</v>
       </c>
-    </row>
-    <row r="212" spans="1:6">
+      <c r="G211" s="1">
+        <v>595.17</v>
+      </c>
+      <c r="H211" s="1">
+        <v>1107.04</v>
+      </c>
+      <c r="I211" s="1">
+        <v>1073.41</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C212" s="1">
         <v>2492.18</v>
@@ -4821,10 +6732,19 @@
       <c r="F212" s="1">
         <v>1631.71</v>
       </c>
-    </row>
-    <row r="213" spans="1:6">
+      <c r="G212" s="1">
+        <v>1904.52</v>
+      </c>
+      <c r="H212" s="1">
+        <v>1716.36</v>
+      </c>
+      <c r="I212" s="1">
+        <v>2235.19</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C213" s="1">
         <v>927.0800000000002</v>
@@ -4833,21 +6753,30 @@
         <v>535.9299999999999</v>
       </c>
       <c r="E213" s="1">
-        <v>950.8900000000001</v>
+        <v>950.89</v>
       </c>
       <c r="F213" s="1">
         <v>659.9299999999999</v>
       </c>
-    </row>
-    <row r="214" spans="1:6">
+      <c r="G213" s="1">
+        <v>1058.71</v>
+      </c>
+      <c r="H213" s="1">
+        <v>1440.18</v>
+      </c>
+      <c r="I213" s="1">
+        <v>1357.23</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C214" s="1">
         <v>673.9100000000001</v>
       </c>
       <c r="D214" s="1">
-        <v>561.8499999999999</v>
+        <v>561.85</v>
       </c>
       <c r="E214" s="1">
         <v>495.91</v>
@@ -4855,10 +6784,19 @@
       <c r="F214" s="1">
         <v>294.11</v>
       </c>
-    </row>
-    <row r="215" spans="1:6">
+      <c r="G214" s="1">
+        <v>650.9200000000001</v>
+      </c>
+      <c r="H214" s="1">
+        <v>398.93</v>
+      </c>
+      <c r="I214" s="1">
+        <v>469.9299999999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C215" s="1">
         <v>1911.77</v>
@@ -4870,12 +6808,21 @@
         <v>1328.85</v>
       </c>
       <c r="F215" s="1">
-        <v>526.85</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
+        <v>526.8499999999999</v>
+      </c>
+      <c r="G215" s="1">
+        <v>1239.19</v>
+      </c>
+      <c r="H215" s="1">
+        <v>1729.5</v>
+      </c>
+      <c r="I215" s="1">
+        <v>1240.29</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C216" s="1">
         <v>1830.39</v>
@@ -4889,10 +6836,19 @@
       <c r="F216" s="1">
         <v>1098.68</v>
       </c>
-    </row>
-    <row r="217" spans="1:6">
+      <c r="G216" s="1">
+        <v>607.8</v>
+      </c>
+      <c r="H216" s="1">
+        <v>2289.1</v>
+      </c>
+      <c r="I216" s="1">
+        <v>1706.64</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C217" s="1">
         <v>1400.54</v>
@@ -4901,38 +6857,56 @@
         <v>1480.93</v>
       </c>
       <c r="E217" s="1">
-        <v>966.6500000000001</v>
+        <v>966.65</v>
       </c>
       <c r="F217" s="1">
         <v>704.6799999999999</v>
       </c>
-    </row>
-    <row r="218" spans="1:6">
+      <c r="G217" s="1">
+        <v>601.6</v>
+      </c>
+      <c r="H217" s="1">
+        <v>1126.37</v>
+      </c>
+      <c r="I217" s="1">
+        <v>834.71</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C218" s="1">
         <v>401.89</v>
       </c>
       <c r="D218" s="1">
-        <v>467.93</v>
+        <v>467.9300000000001</v>
       </c>
       <c r="E218" s="1">
         <v>576.5599999999999</v>
       </c>
       <c r="F218" s="1">
-        <v>502.65</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
+        <v>502.6500000000001</v>
+      </c>
+      <c r="G218" s="1">
+        <v>619.9400000000001</v>
+      </c>
+      <c r="H218" s="1">
+        <v>512.67</v>
+      </c>
+      <c r="I218" s="1">
+        <v>655.2800000000001</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C219" s="1">
         <v>723.92</v>
       </c>
       <c r="D219" s="1">
-        <v>648.8499999999999</v>
+        <v>648.85</v>
       </c>
       <c r="E219" s="1">
         <v>589.6</v>
@@ -4940,10 +6914,19 @@
       <c r="F219" s="1">
         <v>937.52</v>
       </c>
-    </row>
-    <row r="220" spans="1:6">
+      <c r="G219" s="1">
+        <v>1825.86</v>
+      </c>
+      <c r="H219" s="1">
+        <v>1527.98</v>
+      </c>
+      <c r="I219" s="1">
+        <v>794.86</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C220" s="1">
         <v>619.24</v>
@@ -4957,10 +6940,19 @@
       <c r="F220" s="1">
         <v>832.6700000000001</v>
       </c>
-    </row>
-    <row r="221" spans="1:6">
+      <c r="G220" s="1">
+        <v>494.92</v>
+      </c>
+      <c r="H220" s="1">
+        <v>835.7900000000001</v>
+      </c>
+      <c r="I220" s="1">
+        <v>505.71</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C221" s="1">
         <v>2637.8</v>
@@ -4974,27 +6966,45 @@
       <c r="F221" s="1">
         <v>1658.2</v>
       </c>
-    </row>
-    <row r="222" spans="1:6">
+      <c r="G221" s="1">
+        <v>907.7900000000001</v>
+      </c>
+      <c r="H221" s="1">
+        <v>1376.59</v>
+      </c>
+      <c r="I221" s="1">
+        <v>1025.31</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C222" s="1">
-        <v>2737.559999999999</v>
+        <v>2737.56</v>
       </c>
       <c r="D222" s="1">
-        <v>2785.66</v>
+        <v>2785.659999999999</v>
       </c>
       <c r="E222" s="1">
-        <v>3055.649999999999</v>
+        <v>3055.649999999998</v>
       </c>
       <c r="F222" s="1">
         <v>2885.899999999999</v>
       </c>
-    </row>
-    <row r="223" spans="1:6">
+      <c r="G222" s="1">
+        <v>1484.97</v>
+      </c>
+      <c r="H222" s="1">
+        <v>2633.17</v>
+      </c>
+      <c r="I222" s="1">
+        <v>2675.689999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C223" s="1">
         <v>983.96</v>
@@ -5008,10 +7018,19 @@
       <c r="F223" s="1">
         <v>1011.54</v>
       </c>
-    </row>
-    <row r="224" spans="1:6">
+      <c r="G223" s="1">
+        <v>1264.58</v>
+      </c>
+      <c r="H223" s="1">
+        <v>903.9100000000001</v>
+      </c>
+      <c r="I223" s="1">
+        <v>941.1600000000001</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C224" s="1">
         <v>1757.49</v>
@@ -5025,16 +7044,25 @@
       <c r="F224" s="1">
         <v>899.15</v>
       </c>
-    </row>
-    <row r="225" spans="1:6">
+      <c r="G224" s="1">
+        <v>1896.12</v>
+      </c>
+      <c r="H224" s="1">
+        <v>1232.59</v>
+      </c>
+      <c r="I224" s="1">
+        <v>1311.69</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C225" s="1">
         <v>342.83</v>
       </c>
       <c r="D225" s="1">
-        <v>502.2400000000001</v>
+        <v>502.24</v>
       </c>
       <c r="E225" s="1">
         <v>401.08</v>
@@ -5042,10 +7070,19 @@
       <c r="F225" s="1">
         <v>454.92</v>
       </c>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" s="1">
+        <v>664.91</v>
+      </c>
+      <c r="H225" s="1">
+        <v>1218.81</v>
+      </c>
+      <c r="I225" s="1">
+        <v>1100.5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C226" s="1">
         <v>968.25</v>
@@ -5057,12 +7094,21 @@
         <v>736.58</v>
       </c>
       <c r="F226" s="1">
-        <v>402.03</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
+        <v>468.02</v>
+      </c>
+      <c r="G226" s="1">
+        <v>632.1</v>
+      </c>
+      <c r="H226" s="1">
+        <v>1488.71</v>
+      </c>
+      <c r="I226" s="1">
+        <v>1344.66</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C227" s="1">
         <v>3906.889999999999</v>
@@ -5071,15 +7117,24 @@
         <v>3894.5</v>
       </c>
       <c r="E227" s="1">
-        <v>4342.150000000001</v>
+        <v>4342.15</v>
       </c>
       <c r="F227" s="1">
         <v>3267.829999999999</v>
       </c>
-    </row>
-    <row r="228" spans="1:6">
+      <c r="G227" s="1">
+        <v>3091.6</v>
+      </c>
+      <c r="H227" s="1">
+        <v>4555.429999999998</v>
+      </c>
+      <c r="I227" s="1">
+        <v>5148.89</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C228" s="1">
         <v>2118.53</v>
@@ -5093,27 +7148,45 @@
       <c r="F228" s="1">
         <v>1065.04</v>
       </c>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G228" s="1">
+        <v>3948.49</v>
+      </c>
+      <c r="H228" s="1">
+        <v>2263.62</v>
+      </c>
+      <c r="I228" s="1">
+        <v>2249.68</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C229" s="1">
-        <v>736.26</v>
+        <v>736.2600000000001</v>
       </c>
       <c r="D229" s="1">
         <v>902.0300000000001</v>
       </c>
       <c r="E229" s="1">
-        <v>557.29</v>
+        <v>557.2900000000001</v>
       </c>
       <c r="F229" s="1">
         <v>362.93</v>
       </c>
-    </row>
-    <row r="230" spans="1:6">
+      <c r="G229" s="1">
+        <v>796.0200000000001</v>
+      </c>
+      <c r="H229" s="1">
+        <v>595.88</v>
+      </c>
+      <c r="I229" s="1">
+        <v>613.91</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C230" s="1">
         <v>741.38</v>
@@ -5127,16 +7200,25 @@
       <c r="F230" s="1">
         <v>1227.14</v>
       </c>
-    </row>
-    <row r="231" spans="1:6">
+      <c r="G230" s="1">
+        <v>1010.09</v>
+      </c>
+      <c r="H230" s="1">
+        <v>1097.06</v>
+      </c>
+      <c r="I230" s="1">
+        <v>1914.01</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C231" s="1">
         <v>1558.6</v>
       </c>
       <c r="D231" s="1">
-        <v>778.53</v>
+        <v>778.5300000000001</v>
       </c>
       <c r="E231" s="1">
         <v>699.4499999999998</v>
@@ -5144,10 +7226,19 @@
       <c r="F231" s="1">
         <v>1466.47</v>
       </c>
-    </row>
-    <row r="232" spans="1:6">
+      <c r="G231" s="1">
+        <v>1846.43</v>
+      </c>
+      <c r="H231" s="1">
+        <v>1178.5</v>
+      </c>
+      <c r="I231" s="1">
+        <v>959.6700000000001</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C232" s="1">
         <v>1408.15</v>
@@ -5161,13 +7252,22 @@
       <c r="F232" s="1">
         <v>1009.54</v>
       </c>
-    </row>
-    <row r="233" spans="1:6">
+      <c r="G232" s="1">
+        <v>1631.52</v>
+      </c>
+      <c r="H232" s="1">
+        <v>1466.77</v>
+      </c>
+      <c r="I232" s="1">
+        <v>880.9299999999999</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C233" s="1">
-        <v>2620.009999999999</v>
+        <v>2620.01</v>
       </c>
       <c r="D233" s="1">
         <v>1676.9</v>
@@ -5178,27 +7278,45 @@
       <c r="F233" s="1">
         <v>2514.09</v>
       </c>
-    </row>
-    <row r="234" spans="1:6">
+      <c r="G233" s="1">
+        <v>2537.599999999999</v>
+      </c>
+      <c r="H233" s="1">
+        <v>2568.18</v>
+      </c>
+      <c r="I233" s="1">
+        <v>2320.929999999999</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C234" s="1">
         <v>2677.139999999999</v>
       </c>
       <c r="D234" s="1">
-        <v>2587.009999999999</v>
+        <v>2587.01</v>
       </c>
       <c r="E234" s="1">
         <v>2034.94</v>
       </c>
       <c r="F234" s="1">
-        <v>2623.799999999999</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
+        <v>2623.8</v>
+      </c>
+      <c r="G234" s="1">
+        <v>4523.879999999999</v>
+      </c>
+      <c r="H234" s="1">
+        <v>2910.43</v>
+      </c>
+      <c r="I234" s="1">
+        <v>3215.48</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C235" s="1">
         <v>1716.26</v>
@@ -5212,10 +7330,19 @@
       <c r="F235" s="1">
         <v>2705.58</v>
       </c>
-    </row>
-    <row r="236" spans="1:6">
+      <c r="G235" s="1">
+        <v>1548.37</v>
+      </c>
+      <c r="H235" s="1">
+        <v>1740.35</v>
+      </c>
+      <c r="I235" s="1">
+        <v>2257.96</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C236" s="1">
         <v>304.56</v>
@@ -5229,16 +7356,25 @@
       <c r="F236" s="1">
         <v>432.86</v>
       </c>
-    </row>
-    <row r="237" spans="1:6">
+      <c r="G236" s="1">
+        <v>762.27</v>
+      </c>
+      <c r="H236" s="1">
+        <v>717.1799999999999</v>
+      </c>
+      <c r="I236" s="1">
+        <v>160.57</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C237" s="1">
         <v>2649.27</v>
       </c>
       <c r="D237" s="1">
-        <v>3077.37</v>
+        <v>3077.369999999999</v>
       </c>
       <c r="E237" s="1">
         <v>2665.349999999999</v>
@@ -5246,10 +7382,19 @@
       <c r="F237" s="1">
         <v>1993.27</v>
       </c>
-    </row>
-    <row r="238" spans="1:6">
+      <c r="G237" s="1">
+        <v>3079.889999999999</v>
+      </c>
+      <c r="H237" s="1">
+        <v>3430.82</v>
+      </c>
+      <c r="I237" s="1">
+        <v>1901.64</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C238" s="1">
         <v>431.74</v>
@@ -5263,10 +7408,19 @@
       <c r="F238" s="1">
         <v>886.0599999999999</v>
       </c>
-    </row>
-    <row r="239" spans="1:6">
+      <c r="G238" s="1">
+        <v>559.79</v>
+      </c>
+      <c r="H238" s="1">
+        <v>1286.44</v>
+      </c>
+      <c r="I238" s="1">
+        <v>808.8800000000001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C239" s="1">
         <v>1221.52</v>
@@ -5280,10 +7434,19 @@
       <c r="F239" s="1">
         <v>1160.59</v>
       </c>
-    </row>
-    <row r="240" spans="1:6">
+      <c r="G239" s="1">
+        <v>376.93</v>
+      </c>
+      <c r="H239" s="1">
+        <v>1246.58</v>
+      </c>
+      <c r="I239" s="1">
+        <v>777.38</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C240" s="1">
         <v>942.73</v>
@@ -5297,30 +7460,48 @@
       <c r="F240" s="1">
         <v>804.98</v>
       </c>
-    </row>
-    <row r="241" spans="1:6">
+      <c r="G240" s="1">
+        <v>664.1600000000001</v>
+      </c>
+      <c r="H240" s="1">
+        <v>645.52</v>
+      </c>
+      <c r="I240" s="1">
+        <v>1256.28</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C241" s="1">
-        <v>734.91</v>
+        <v>734.9100000000001</v>
       </c>
       <c r="D241" s="1">
-        <v>350.8499999999999</v>
+        <v>350.85</v>
       </c>
       <c r="E241" s="1">
         <v>835.62</v>
       </c>
       <c r="F241" s="1">
-        <v>568.4100000000001</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
+        <v>568.41</v>
+      </c>
+      <c r="G241" s="1">
+        <v>627.96</v>
+      </c>
+      <c r="H241" s="1">
+        <v>1076.34</v>
+      </c>
+      <c r="I241" s="1">
+        <v>250.96</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C242" s="1">
-        <v>2725.51</v>
+        <v>2725.509999999999</v>
       </c>
       <c r="D242" s="1">
         <v>3009.819999999999</v>
@@ -5331,13 +7512,22 @@
       <c r="F242" s="1">
         <v>2038.72</v>
       </c>
-    </row>
-    <row r="243" spans="1:6">
+      <c r="G242" s="1">
+        <v>2942.07</v>
+      </c>
+      <c r="H242" s="1">
+        <v>3212.739999999999</v>
+      </c>
+      <c r="I242" s="1">
+        <v>3734.409999999999</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C243" s="1">
-        <v>3170.239999999999</v>
+        <v>3170.24</v>
       </c>
       <c r="D243" s="1">
         <v>3704.45</v>
@@ -5348,10 +7538,19 @@
       <c r="F243" s="1">
         <v>5251.52</v>
       </c>
-    </row>
-    <row r="244" spans="1:6">
+      <c r="G243" s="1">
+        <v>4139.9</v>
+      </c>
+      <c r="H243" s="1">
+        <v>2854.219999999999</v>
+      </c>
+      <c r="I243" s="1">
+        <v>3933.4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C244" s="1">
         <v>940.27</v>
@@ -5363,18 +7562,27 @@
         <v>648</v>
       </c>
       <c r="F244" s="1">
-        <v>894.1200000000001</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
+        <v>894.12</v>
+      </c>
+      <c r="G244" s="1">
+        <v>822.8000000000002</v>
+      </c>
+      <c r="H244" s="1">
+        <v>1092.2</v>
+      </c>
+      <c r="I244" s="1">
+        <v>2003.78</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C245" s="1">
-        <v>3081.76</v>
+        <v>3081.759999999999</v>
       </c>
       <c r="D245" s="1">
-        <v>2588.239999999998</v>
+        <v>2588.24</v>
       </c>
       <c r="E245" s="1">
         <v>1991.95</v>
@@ -5382,16 +7590,25 @@
       <c r="F245" s="1">
         <v>2300.9</v>
       </c>
-    </row>
-    <row r="246" spans="1:6">
+      <c r="G245" s="1">
+        <v>3590.819999999999</v>
+      </c>
+      <c r="H245" s="1">
+        <v>2372.35</v>
+      </c>
+      <c r="I245" s="1">
+        <v>3748.899999999999</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C246" s="1">
-        <v>2227.56</v>
+        <v>2227.559999999999</v>
       </c>
       <c r="D246" s="1">
-        <v>2801.3</v>
+        <v>2801.299999999999</v>
       </c>
       <c r="E246" s="1">
         <v>2166.29</v>
@@ -5399,10 +7616,19 @@
       <c r="F246" s="1">
         <v>1527.43</v>
       </c>
-    </row>
-    <row r="247" spans="1:6">
+      <c r="G246" s="1">
+        <v>3174.369999999999</v>
+      </c>
+      <c r="H246" s="1">
+        <v>3514.23</v>
+      </c>
+      <c r="I246" s="1">
+        <v>2773.109999999999</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C247" s="1">
         <v>1403.31</v>
@@ -5416,10 +7642,19 @@
       <c r="F247" s="1">
         <v>1854.42</v>
       </c>
-    </row>
-    <row r="248" spans="1:6">
+      <c r="G247" s="1">
+        <v>1475.49</v>
+      </c>
+      <c r="H247" s="1">
+        <v>791.1700000000001</v>
+      </c>
+      <c r="I247" s="1">
+        <v>1333.78</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C248" s="1">
         <v>3099.319999999999</v>
@@ -5433,13 +7668,22 @@
       <c r="F248" s="1">
         <v>1830.16</v>
       </c>
-    </row>
-    <row r="249" spans="1:6">
+      <c r="G248" s="1">
+        <v>2602.43</v>
+      </c>
+      <c r="H248" s="1">
+        <v>1905.34</v>
+      </c>
+      <c r="I248" s="1">
+        <v>3527.04</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C249" s="1">
-        <v>696.02</v>
+        <v>696.0200000000001</v>
       </c>
       <c r="D249" s="1">
         <v>1747.57</v>
@@ -5450,13 +7694,22 @@
       <c r="F249" s="1">
         <v>1555.28</v>
       </c>
-    </row>
-    <row r="250" spans="1:6">
+      <c r="G249" s="1">
+        <v>1729.49</v>
+      </c>
+      <c r="H249" s="1">
+        <v>1477.74</v>
+      </c>
+      <c r="I249" s="1">
+        <v>1953.28</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C250" s="1">
-        <v>2785.299999999999</v>
+        <v>2785.3</v>
       </c>
       <c r="D250" s="1">
         <v>2074.67</v>
@@ -5465,12 +7718,21 @@
         <v>2327.68</v>
       </c>
       <c r="F250" s="1">
-        <v>3074.15</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
+        <v>3164.14</v>
+      </c>
+      <c r="G250" s="1">
+        <v>1962.1</v>
+      </c>
+      <c r="H250" s="1">
+        <v>2271.64</v>
+      </c>
+      <c r="I250" s="1">
+        <v>1968.37</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C251" s="1">
         <v>677.1</v>
@@ -5484,10 +7746,19 @@
       <c r="F251" s="1">
         <v>1256.69</v>
       </c>
-    </row>
-    <row r="252" spans="1:6">
+      <c r="G251" s="1">
+        <v>581.52</v>
+      </c>
+      <c r="H251" s="1">
+        <v>1469.09</v>
+      </c>
+      <c r="I251" s="1">
+        <v>2077.53</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C252" s="1">
         <v>355.45</v>
@@ -5496,15 +7767,24 @@
         <v>260.5</v>
       </c>
       <c r="E252" s="1">
-        <v>690.9</v>
+        <v>690.9000000000001</v>
       </c>
       <c r="F252" s="1">
         <v>332.96</v>
       </c>
-    </row>
-    <row r="253" spans="1:6">
+      <c r="G252" s="1">
+        <v>385.42</v>
+      </c>
+      <c r="H252" s="1">
+        <v>336.9000000000001</v>
+      </c>
+      <c r="I252" s="1">
+        <v>395.95</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C253" s="1">
         <v>1655.58</v>
@@ -5518,10 +7798,19 @@
       <c r="F253" s="1">
         <v>1091.73</v>
       </c>
-    </row>
-    <row r="254" spans="1:6">
+      <c r="G253" s="1">
+        <v>1147.31</v>
+      </c>
+      <c r="H253" s="1">
+        <v>1651.57</v>
+      </c>
+      <c r="I253" s="1">
+        <v>2062.26</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C254" s="1">
         <v>772.91</v>
@@ -5535,13 +7824,22 @@
       <c r="F254" s="1">
         <v>340.95</v>
       </c>
-    </row>
-    <row r="255" spans="1:6">
+      <c r="G254" s="1">
+        <v>690.6999999999998</v>
+      </c>
+      <c r="H254" s="1">
+        <v>577.97</v>
+      </c>
+      <c r="I254" s="1">
+        <v>372.93</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C255" s="1">
-        <v>2909.05</v>
+        <v>2909.049999999999</v>
       </c>
       <c r="D255" s="1">
         <v>2125.64</v>
@@ -5552,10 +7850,19 @@
       <c r="F255" s="1">
         <v>2079.76</v>
       </c>
-    </row>
-    <row r="256" spans="1:6">
+      <c r="G255" s="1">
+        <v>1426.46</v>
+      </c>
+      <c r="H255" s="1">
+        <v>2464.2</v>
+      </c>
+      <c r="I255" s="1">
+        <v>2504.81</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C256" s="1">
         <v>483.91</v>
@@ -5569,10 +7876,19 @@
       <c r="F256" s="1">
         <v>832.8900000000001</v>
       </c>
-    </row>
-    <row r="257" spans="1:6">
+      <c r="G256" s="1">
+        <v>746.72</v>
+      </c>
+      <c r="H256" s="1">
+        <v>424.45</v>
+      </c>
+      <c r="I256" s="1">
+        <v>378.84</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C257" s="1">
         <v>1980.78</v>
@@ -5586,16 +7902,25 @@
       <c r="F257" s="1">
         <v>1179.07</v>
       </c>
-    </row>
-    <row r="258" spans="1:6">
+      <c r="G257" s="1">
+        <v>1578.95</v>
+      </c>
+      <c r="H257" s="1">
+        <v>2975.75</v>
+      </c>
+      <c r="I257" s="1">
+        <v>1706.08</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C258" s="1">
         <v>371.18</v>
       </c>
       <c r="D258" s="1">
-        <v>967.5200000000002</v>
+        <v>967.5200000000001</v>
       </c>
       <c r="E258" s="1">
         <v>489.47</v>
@@ -5603,10 +7928,19 @@
       <c r="F258" s="1">
         <v>311.97</v>
       </c>
-    </row>
-    <row r="259" spans="1:6">
+      <c r="G258" s="1">
+        <v>339.25</v>
+      </c>
+      <c r="H258" s="1">
+        <v>638.48</v>
+      </c>
+      <c r="I258" s="1">
+        <v>275.98</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C259" s="1">
         <v>2200.71</v>
@@ -5620,33 +7954,51 @@
       <c r="F259" s="1">
         <v>1483.58</v>
       </c>
-    </row>
-    <row r="260" spans="1:6">
+      <c r="G259" s="1">
+        <v>1528.79</v>
+      </c>
+      <c r="H259" s="1">
+        <v>1276.43</v>
+      </c>
+      <c r="I259" s="1">
+        <v>2275.47</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C260" s="1">
         <v>2491.63</v>
       </c>
       <c r="D260" s="1">
-        <v>2879.089999999999</v>
+        <v>2879.09</v>
       </c>
       <c r="E260" s="1">
-        <v>3999.059999999999</v>
+        <v>3999.06</v>
       </c>
       <c r="F260" s="1">
-        <v>2749.659999999999</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+        <v>2749.66</v>
+      </c>
+      <c r="G260" s="1">
+        <v>3023.309999999999</v>
+      </c>
+      <c r="H260" s="1">
+        <v>2624.260000000001</v>
+      </c>
+      <c r="I260" s="1">
+        <v>2801.78</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C261" s="1">
         <v>1482.86</v>
       </c>
       <c r="D261" s="1">
-        <v>2299.619999999999</v>
+        <v>2299.62</v>
       </c>
       <c r="E261" s="1">
         <v>1383.51</v>
@@ -5654,30 +8006,48 @@
       <c r="F261" s="1">
         <v>1317.73</v>
       </c>
-    </row>
-    <row r="262" spans="1:6">
+      <c r="G261" s="1">
+        <v>1746.54</v>
+      </c>
+      <c r="H261" s="1">
+        <v>1269.59</v>
+      </c>
+      <c r="I261" s="1">
+        <v>3677.989999999999</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C262" s="1">
         <v>5970.049999999998</v>
       </c>
       <c r="D262" s="1">
-        <v>4359.049999999999</v>
+        <v>4359.049999999998</v>
       </c>
       <c r="E262" s="1">
-        <v>3965.699999999999</v>
+        <v>3965.7</v>
       </c>
       <c r="F262" s="1">
         <v>4555.289999999999</v>
       </c>
-    </row>
-    <row r="263" spans="1:6">
+      <c r="G262" s="1">
+        <v>4416.329999999999</v>
+      </c>
+      <c r="H262" s="1">
+        <v>5211.449999999998</v>
+      </c>
+      <c r="I262" s="1">
+        <v>3874.029999999999</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C263" s="1">
-        <v>2840.719999999999</v>
+        <v>2840.720000000001</v>
       </c>
       <c r="D263" s="1">
         <v>2332.73</v>
@@ -5688,10 +8058,19 @@
       <c r="F263" s="1">
         <v>2408.049999999999</v>
       </c>
-    </row>
-    <row r="264" spans="1:6">
+      <c r="G263" s="1">
+        <v>2995.169999999999</v>
+      </c>
+      <c r="H263" s="1">
+        <v>1890.89</v>
+      </c>
+      <c r="I263" s="1">
+        <v>4225.579999999998</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C264" s="1">
         <v>1921.94</v>
@@ -5705,33 +8084,51 @@
       <c r="F264" s="1">
         <v>1207.02</v>
       </c>
-    </row>
-    <row r="265" spans="1:6">
+      <c r="G264" s="1">
+        <v>1396.57</v>
+      </c>
+      <c r="H264" s="1">
+        <v>1946.98</v>
+      </c>
+      <c r="I264" s="1">
+        <v>2382.74</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C265" s="1">
-        <v>5651.999999999998</v>
+        <v>5652</v>
       </c>
       <c r="D265" s="1">
-        <v>6377.179999999998</v>
+        <v>6377.179999999996</v>
       </c>
       <c r="E265" s="1">
-        <v>6019.36</v>
+        <v>6019.359999999999</v>
       </c>
       <c r="F265" s="1">
-        <v>4101.400000000001</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
+        <v>4101.4</v>
+      </c>
+      <c r="G265" s="1">
+        <v>4719.549999999999</v>
+      </c>
+      <c r="H265" s="1">
+        <v>7862.259999999998</v>
+      </c>
+      <c r="I265" s="1">
+        <v>8146.11</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C266" s="1">
         <v>4295.019999999999</v>
       </c>
       <c r="D266" s="1">
-        <v>2671.53</v>
+        <v>2671.529999999999</v>
       </c>
       <c r="E266" s="1">
         <v>3723.309999999999</v>
@@ -5739,10 +8136,19 @@
       <c r="F266" s="1">
         <v>3016.59</v>
       </c>
-    </row>
-    <row r="267" spans="1:6">
+      <c r="G266" s="1">
+        <v>3571.299999999998</v>
+      </c>
+      <c r="H266" s="1">
+        <v>4084.639999999999</v>
+      </c>
+      <c r="I266" s="1">
+        <v>3320.669999999999</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C267" s="1">
         <v>2283.95</v>
@@ -5756,10 +8162,19 @@
       <c r="F267" s="1">
         <v>2380.78</v>
       </c>
-    </row>
-    <row r="268" spans="1:6">
+      <c r="G267" s="1">
+        <v>3498.169999999998</v>
+      </c>
+      <c r="H267" s="1">
+        <v>3078.519999999999</v>
+      </c>
+      <c r="I267" s="1">
+        <v>2868.65</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C268" s="1">
         <v>1441.43</v>
@@ -5773,10 +8188,19 @@
       <c r="F268" s="1">
         <v>1572.59</v>
       </c>
-    </row>
-    <row r="269" spans="1:6">
+      <c r="G268" s="1">
+        <v>282.4900000000001</v>
+      </c>
+      <c r="H268" s="1">
+        <v>1695.64</v>
+      </c>
+      <c r="I268" s="1">
+        <v>748.7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C269" s="1">
         <v>737.27</v>
@@ -5790,26 +8214,70 @@
       <c r="F269" s="1">
         <v>702.01</v>
       </c>
-    </row>
-    <row r="270" spans="1:6">
+      <c r="G269" s="1">
+        <v>1220.79</v>
+      </c>
+      <c r="H269" s="1">
+        <v>950.4200000000001</v>
+      </c>
+      <c r="I269" s="1">
+        <v>1097.35</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>275</v>
-      </c>
-      <c r="C270" s="1">
+        <v>278</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H270" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I270" s="1">
+        <v>123.49</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" t="s">
+        <v>279</v>
+      </c>
+      <c r="C271" s="1">
         <v>1204.39</v>
       </c>
-      <c r="D270" s="1">
+      <c r="D271" s="1">
         <v>1082.42</v>
       </c>
-      <c r="E270" s="1">
+      <c r="E271" s="1">
         <v>1268.22</v>
       </c>
-      <c r="F270" s="1">
+      <c r="F271" s="1">
         <v>1469.32</v>
       </c>
+      <c r="G271" s="1">
+        <v>1559.01</v>
+      </c>
+      <c r="H271" s="1">
+        <v>497.92</v>
+      </c>
+      <c r="I271" s="1">
+        <v>256.6</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="269">
+  <mergeCells count="270">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -6079,6 +8547,7 @@
     <mergeCell ref="A268:B268"/>
     <mergeCell ref="A269:B269"/>
     <mergeCell ref="A270:B270"/>
+    <mergeCell ref="A271:B271"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
